--- a/AAII_Financials/Quarterly/CVAT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CVAT_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="92">
   <si>
     <t>CVAT</t>
   </si>
@@ -656,152 +656,155 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AG102"/>
+  <dimension ref="A5:AH102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43738</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43646</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43555</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43465</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43373</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43281</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43190</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43100</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43008</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>42916</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42825</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42735</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42643</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>10</v>
+      <c r="D8" s="3">
+        <v>200</v>
       </c>
       <c r="E8" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F8" s="3">
         <v>100</v>
@@ -810,93 +813,96 @@
         <v>100</v>
       </c>
       <c r="H8" s="3">
+        <v>100</v>
+      </c>
+      <c r="I8" s="3">
         <v>300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1000</v>
       </c>
-      <c r="J8" s="3">
-        <v>0</v>
-      </c>
       <c r="K8" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L8" s="3">
+        <v>100</v>
+      </c>
+      <c r="M8" s="3">
         <v>600</v>
       </c>
-      <c r="M8" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="N8" s="3">
-        <v>100</v>
+      <c r="N8" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="O8" s="3">
         <v>100</v>
       </c>
       <c r="P8" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q8" s="3">
         <v>400</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>300</v>
       </c>
-      <c r="S8" s="3">
-        <v>0</v>
-      </c>
       <c r="T8" s="3">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="U8" s="3">
         <v>400</v>
       </c>
       <c r="V8" s="3">
+        <v>400</v>
+      </c>
+      <c r="W8" s="3">
         <v>300</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>400</v>
       </c>
-      <c r="X8" s="3">
-        <v>100</v>
-      </c>
       <c r="Y8" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="Z8" s="3">
         <v>300</v>
       </c>
       <c r="AA8" s="3">
+        <v>300</v>
+      </c>
+      <c r="AB8" s="3">
         <v>700</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>300</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>400</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>1400</v>
       </c>
-      <c r="AE8" s="3">
-        <v>100</v>
-      </c>
       <c r="AF8" s="3">
         <v>100</v>
       </c>
       <c r="AG8" s="3">
+        <v>100</v>
+      </c>
+      <c r="AH8" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E9" s="3">
-        <v>0</v>
+      <c r="D9" s="3">
+        <v>0</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="F9" s="3">
         <v>0</v>
@@ -905,10 +911,10 @@
         <v>0</v>
       </c>
       <c r="H9" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I9" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J9" s="3">
         <v>0</v>
@@ -937,11 +943,11 @@
       <c r="R9" s="3">
         <v>0</v>
       </c>
-      <c r="S9" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="T9" s="3">
-        <v>0</v>
+      <c r="S9" s="3">
+        <v>0</v>
+      </c>
+      <c r="T9" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="U9" s="3">
         <v>0</v>
@@ -956,10 +962,10 @@
         <v>0</v>
       </c>
       <c r="Y9" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Z9" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AA9" s="3">
         <v>0</v>
@@ -982,16 +988,19 @@
       <c r="AG9" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH9" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E10" s="3">
-        <v>100</v>
+      <c r="D10" s="3">
+        <v>200</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="F10" s="3">
         <v>100</v>
@@ -1000,85 +1009,88 @@
         <v>100</v>
       </c>
       <c r="H10" s="3">
+        <v>100</v>
+      </c>
+      <c r="I10" s="3">
         <v>300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1000</v>
       </c>
-      <c r="J10" s="3">
-        <v>0</v>
-      </c>
       <c r="K10" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L10" s="3">
+        <v>100</v>
+      </c>
+      <c r="M10" s="3">
         <v>600</v>
       </c>
-      <c r="M10" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="N10" s="3">
-        <v>100</v>
+      <c r="N10" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="O10" s="3">
         <v>100</v>
       </c>
       <c r="P10" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q10" s="3">
         <v>400</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>1000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>300</v>
       </c>
-      <c r="S10" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="T10" s="3">
-        <v>400</v>
+      <c r="T10" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="U10" s="3">
         <v>400</v>
       </c>
       <c r="V10" s="3">
+        <v>400</v>
+      </c>
+      <c r="W10" s="3">
         <v>300</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>400</v>
       </c>
-      <c r="X10" s="3">
-        <v>100</v>
-      </c>
       <c r="Y10" s="3">
+        <v>100</v>
+      </c>
+      <c r="Z10" s="3">
         <v>200</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>300</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>700</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>300</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>400</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>1400</v>
       </c>
-      <c r="AE10" s="3">
-        <v>100</v>
-      </c>
       <c r="AF10" s="3">
         <v>100</v>
       </c>
       <c r="AG10" s="3">
+        <v>100</v>
+      </c>
+      <c r="AH10" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1112,19 +1124,20 @@
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
-    </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH11" s="3"/>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="3">
-        <v>0</v>
+      <c r="D12" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="E12" s="3">
         <v>0</v>
       </c>
-      <c r="F12" s="3" t="s">
-        <v>10</v>
+      <c r="F12" s="3">
+        <v>0</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>10</v>
@@ -1132,8 +1145,8 @@
       <c r="H12" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="I12" s="3">
-        <v>0</v>
+      <c r="I12" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="J12" s="3">
         <v>0</v>
@@ -1141,17 +1154,17 @@
       <c r="K12" s="3">
         <v>0</v>
       </c>
-      <c r="L12" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="M12" s="3">
-        <v>0</v>
-      </c>
-      <c r="N12" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="O12" s="3">
-        <v>0</v>
+      <c r="L12" s="3">
+        <v>0</v>
+      </c>
+      <c r="M12" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="N12" s="3">
+        <v>0</v>
+      </c>
+      <c r="O12" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="P12" s="3">
         <v>0</v>
@@ -1207,8 +1220,11 @@
       <c r="AG12" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH12" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1302,16 +1318,19 @@
       <c r="AG13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E14" s="3">
-        <v>0</v>
+      <c r="E14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="F14" s="3">
         <v>0</v>
@@ -1323,20 +1342,20 @@
         <v>0</v>
       </c>
       <c r="I14" s="3">
+        <v>0</v>
+      </c>
+      <c r="J14" s="3">
         <v>200</v>
       </c>
-      <c r="J14" s="3">
-        <v>0</v>
-      </c>
       <c r="K14" s="3">
         <v>0</v>
       </c>
       <c r="L14" s="3">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3">
         <v>-100</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="N14" s="3" t="s">
         <v>10</v>
       </c>
@@ -1352,8 +1371,8 @@
       <c r="R14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
+      <c r="S14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="T14" s="3">
         <v>0</v>
@@ -1367,23 +1386,23 @@
       <c r="W14" s="3">
         <v>0</v>
       </c>
-      <c r="X14" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="Y14" s="3">
-        <v>0</v>
+      <c r="X14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="Z14" s="3">
         <v>0</v>
       </c>
       <c r="AA14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB14" s="3">
         <v>-100</v>
       </c>
-      <c r="AB14" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AC14" s="3">
-        <v>0</v>
+      <c r="AC14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AD14" s="3">
         <v>0</v>
@@ -1391,14 +1410,17 @@
       <c r="AE14" s="3">
         <v>0</v>
       </c>
-      <c r="AF14" s="3" t="s">
-        <v>10</v>
+      <c r="AF14" s="3">
+        <v>0</v>
       </c>
       <c r="AG14" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH14" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1459,8 +1481,8 @@
       <c r="V15" s="3">
         <v>0</v>
       </c>
-      <c r="W15" s="3" t="s">
-        <v>10</v>
+      <c r="W15" s="3">
+        <v>0</v>
       </c>
       <c r="X15" s="3" t="s">
         <v>10</v>
@@ -1471,8 +1493,8 @@
       <c r="Z15" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AA15" s="3">
-        <v>0</v>
+      <c r="AA15" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AB15" s="3">
         <v>0</v>
@@ -1492,8 +1514,11 @@
       <c r="AG15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1524,19 +1549,20 @@
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
-    </row>
-    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH16" s="3"/>
+    </row>
+    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>200</v>
+      </c>
+      <c r="E17" s="3">
         <v>300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>400</v>
-      </c>
-      <c r="F17" s="3">
-        <v>300</v>
       </c>
       <c r="G17" s="3">
         <v>300</v>
@@ -1545,22 +1571,22 @@
         <v>300</v>
       </c>
       <c r="I17" s="3">
+        <v>300</v>
+      </c>
+      <c r="J17" s="3">
         <v>800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>200</v>
       </c>
-      <c r="M17" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="N17" s="3">
-        <v>300</v>
+      <c r="N17" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="O17" s="3">
         <v>300</v>
@@ -1575,147 +1601,153 @@
         <v>300</v>
       </c>
       <c r="S17" s="3">
+        <v>300</v>
+      </c>
+      <c r="T17" s="3">
         <v>600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>300</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>400</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>300</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1100</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>300</v>
-      </c>
-      <c r="Y17" s="3">
-        <v>400</v>
       </c>
       <c r="Z17" s="3">
         <v>400</v>
       </c>
       <c r="AA17" s="3">
+        <v>400</v>
+      </c>
+      <c r="AB17" s="3">
         <v>700</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>500</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>700</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>800</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>600</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>300</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>10</v>
+      <c r="D18" s="3">
+        <v>0</v>
       </c>
       <c r="E18" s="3">
         <v>-300</v>
       </c>
       <c r="F18" s="3">
-        <v>-200</v>
+        <v>-300</v>
       </c>
       <c r="G18" s="3">
         <v>-200</v>
       </c>
       <c r="H18" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="I18" s="3">
+        <v>0</v>
+      </c>
+      <c r="J18" s="3">
         <v>200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>400</v>
       </c>
-      <c r="M18" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="N18" s="3">
-        <v>-200</v>
+      <c r="N18" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="O18" s="3">
         <v>-200</v>
       </c>
       <c r="P18" s="3">
-        <v>100</v>
+        <v>-200</v>
       </c>
       <c r="Q18" s="3">
+        <v>100</v>
+      </c>
+      <c r="R18" s="3">
         <v>700</v>
       </c>
-      <c r="R18" s="3">
-        <v>0</v>
-      </c>
       <c r="S18" s="3">
+        <v>0</v>
+      </c>
+      <c r="T18" s="3">
         <v>-600</v>
       </c>
-      <c r="T18" s="3">
-        <v>100</v>
-      </c>
       <c r="U18" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V18" s="3">
         <v>0</v>
       </c>
       <c r="W18" s="3">
+        <v>0</v>
+      </c>
+      <c r="X18" s="3">
         <v>-700</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-200</v>
-      </c>
-      <c r="Y18" s="3">
-        <v>-100</v>
       </c>
       <c r="Z18" s="3">
         <v>-100</v>
       </c>
       <c r="AA18" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AB18" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC18" s="3">
         <v>-200</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-300</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>600</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-500</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-200</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1749,19 +1781,20 @@
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
-    </row>
-    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH19" s="3"/>
+    </row>
+    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>10</v>
+      <c r="D20" s="3">
+        <v>0</v>
       </c>
       <c r="E20" s="3">
+        <v>0</v>
+      </c>
+      <c r="F20" s="3">
         <v>-1200</v>
-      </c>
-      <c r="F20" s="3">
-        <v>-100</v>
       </c>
       <c r="G20" s="3">
         <v>-100</v>
@@ -1773,19 +1806,19 @@
         <v>-100</v>
       </c>
       <c r="J20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="K20" s="3">
         <v>-300</v>
       </c>
-      <c r="K20" s="3">
-        <v>0</v>
-      </c>
       <c r="L20" s="3">
         <v>0</v>
       </c>
-      <c r="M20" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="N20" s="3">
-        <v>0</v>
+      <c r="M20" s="3">
+        <v>0</v>
+      </c>
+      <c r="N20" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="O20" s="3">
         <v>0</v>
@@ -1844,62 +1877,65 @@
       <c r="AG20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E21" s="3">
+      <c r="E21" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F21" s="3">
         <v>-1400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-200</v>
       </c>
-      <c r="G21" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="H21" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="I21" s="3">
-        <v>100</v>
+      <c r="I21" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="J21" s="3">
+        <v>100</v>
+      </c>
+      <c r="K21" s="3">
         <v>-600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>300</v>
       </c>
-      <c r="M21" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="N21" s="3">
+      <c r="N21" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="O21" s="3">
         <v>-100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-200</v>
       </c>
-      <c r="P21" s="3">
-        <v>100</v>
-      </c>
       <c r="Q21" s="3">
+        <v>100</v>
+      </c>
+      <c r="R21" s="3">
         <v>700</v>
       </c>
-      <c r="R21" s="3">
-        <v>0</v>
-      </c>
       <c r="S21" s="3">
+        <v>0</v>
+      </c>
+      <c r="T21" s="3">
         <v>-500</v>
       </c>
-      <c r="T21" s="3">
-        <v>0</v>
-      </c>
       <c r="U21" s="3">
         <v>0</v>
       </c>
@@ -1907,40 +1943,43 @@
         <v>0</v>
       </c>
       <c r="W21" s="3">
+        <v>0</v>
+      </c>
+      <c r="X21" s="3">
         <v>-700</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-200</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-100</v>
       </c>
-      <c r="Z21" s="3">
-        <v>0</v>
-      </c>
       <c r="AA21" s="3">
         <v>0</v>
       </c>
       <c r="AB21" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC21" s="3">
         <v>-100</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>-300</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>600</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>-500</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>-200</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1980,8 +2019,8 @@
       <c r="O22" s="3">
         <v>0</v>
       </c>
-      <c r="P22" s="3" t="s">
-        <v>10</v>
+      <c r="P22" s="3">
+        <v>0</v>
       </c>
       <c r="Q22" s="3" t="s">
         <v>10</v>
@@ -1998,8 +2037,8 @@
       <c r="U22" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="V22" s="3">
-        <v>0</v>
+      <c r="V22" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="W22" s="3">
         <v>0</v>
@@ -2022,74 +2061,77 @@
       <c r="AC22" s="3">
         <v>0</v>
       </c>
-      <c r="AD22" s="3" t="s">
-        <v>10</v>
+      <c r="AD22" s="3">
+        <v>0</v>
       </c>
       <c r="AE22" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AF22" s="3">
-        <v>0</v>
+      <c r="AF22" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AG22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>0</v>
+      </c>
+      <c r="E23" s="3">
         <v>-300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-1400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-100</v>
       </c>
-      <c r="I23" s="3">
-        <v>100</v>
-      </c>
       <c r="J23" s="3">
+        <v>100</v>
+      </c>
+      <c r="K23" s="3">
         <v>-600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-200</v>
       </c>
-      <c r="P23" s="3">
-        <v>100</v>
-      </c>
       <c r="Q23" s="3">
+        <v>100</v>
+      </c>
+      <c r="R23" s="3">
         <v>700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-600</v>
       </c>
-      <c r="T23" s="3">
-        <v>0</v>
-      </c>
       <c r="U23" s="3">
         <v>0</v>
       </c>
@@ -2097,13 +2139,13 @@
         <v>0</v>
       </c>
       <c r="W23" s="3">
+        <v>0</v>
+      </c>
+      <c r="X23" s="3">
         <v>-700</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-300</v>
-      </c>
-      <c r="Y23" s="3">
-        <v>-100</v>
       </c>
       <c r="Z23" s="3">
         <v>-100</v>
@@ -2115,22 +2157,25 @@
         <v>-100</v>
       </c>
       <c r="AC23" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AD23" s="3">
         <v>-300</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>600</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-500</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-200</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2224,8 +2269,11 @@
       <c r="AG24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2319,62 +2367,65 @@
       <c r="AG25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>0</v>
+      </c>
+      <c r="E26" s="3">
         <v>-300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-1400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-100</v>
       </c>
-      <c r="I26" s="3">
-        <v>100</v>
-      </c>
       <c r="J26" s="3">
+        <v>100</v>
+      </c>
+      <c r="K26" s="3">
         <v>-600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>300</v>
       </c>
-      <c r="M26" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="N26" s="3">
+      <c r="N26" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="O26" s="3">
         <v>-100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-200</v>
       </c>
-      <c r="P26" s="3">
-        <v>100</v>
-      </c>
       <c r="Q26" s="3">
+        <v>100</v>
+      </c>
+      <c r="R26" s="3">
         <v>700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-600</v>
       </c>
-      <c r="T26" s="3">
-        <v>0</v>
-      </c>
       <c r="U26" s="3">
         <v>0</v>
       </c>
@@ -2382,13 +2433,13 @@
         <v>0</v>
       </c>
       <c r="W26" s="3">
+        <v>0</v>
+      </c>
+      <c r="X26" s="3">
         <v>-700</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-300</v>
-      </c>
-      <c r="Y26" s="3">
-        <v>-100</v>
       </c>
       <c r="Z26" s="3">
         <v>-100</v>
@@ -2400,76 +2451,79 @@
         <v>-100</v>
       </c>
       <c r="AC26" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AD26" s="3">
         <v>-300</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>600</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-500</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-200</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>0</v>
+      </c>
+      <c r="E27" s="3">
         <v>-300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-1400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-100</v>
       </c>
-      <c r="I27" s="3">
-        <v>100</v>
-      </c>
       <c r="J27" s="3">
+        <v>100</v>
+      </c>
+      <c r="K27" s="3">
         <v>-600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>300</v>
       </c>
-      <c r="M27" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="N27" s="3">
+      <c r="N27" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="O27" s="3">
         <v>-100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-200</v>
       </c>
-      <c r="P27" s="3">
-        <v>100</v>
-      </c>
       <c r="Q27" s="3">
+        <v>100</v>
+      </c>
+      <c r="R27" s="3">
         <v>700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-600</v>
       </c>
-      <c r="T27" s="3">
-        <v>0</v>
-      </c>
       <c r="U27" s="3">
         <v>0</v>
       </c>
@@ -2477,13 +2531,13 @@
         <v>0</v>
       </c>
       <c r="W27" s="3">
+        <v>0</v>
+      </c>
+      <c r="X27" s="3">
         <v>-700</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-300</v>
-      </c>
-      <c r="Y27" s="3">
-        <v>-100</v>
       </c>
       <c r="Z27" s="3">
         <v>-100</v>
@@ -2495,22 +2549,25 @@
         <v>-100</v>
       </c>
       <c r="AC27" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AD27" s="3">
         <v>-300</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>600</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-500</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-200</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2604,8 +2661,11 @@
       <c r="AG28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2699,8 +2759,11 @@
       <c r="AG29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2794,8 +2857,11 @@
       <c r="AG30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2889,20 +2955,23 @@
       <c r="AG31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>10</v>
+      <c r="D32" s="3">
+        <v>0</v>
       </c>
       <c r="E32" s="3">
+        <v>0</v>
+      </c>
+      <c r="F32" s="3">
         <v>1200</v>
       </c>
-      <c r="F32" s="3">
-        <v>100</v>
-      </c>
       <c r="G32" s="3">
         <v>100</v>
       </c>
@@ -2913,19 +2982,19 @@
         <v>100</v>
       </c>
       <c r="J32" s="3">
+        <v>100</v>
+      </c>
+      <c r="K32" s="3">
         <v>300</v>
       </c>
-      <c r="K32" s="3">
-        <v>0</v>
-      </c>
       <c r="L32" s="3">
         <v>0</v>
       </c>
-      <c r="M32" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="N32" s="3">
-        <v>0</v>
+      <c r="M32" s="3">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="O32" s="3">
         <v>0</v>
@@ -2984,62 +3053,65 @@
       <c r="AG32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>0</v>
+      </c>
+      <c r="E33" s="3">
         <v>-300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-1400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-100</v>
       </c>
-      <c r="I33" s="3">
-        <v>100</v>
-      </c>
       <c r="J33" s="3">
+        <v>100</v>
+      </c>
+      <c r="K33" s="3">
         <v>-600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>300</v>
       </c>
-      <c r="M33" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="N33" s="3">
+      <c r="N33" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="O33" s="3">
         <v>-100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-200</v>
       </c>
-      <c r="P33" s="3">
-        <v>100</v>
-      </c>
       <c r="Q33" s="3">
+        <v>100</v>
+      </c>
+      <c r="R33" s="3">
         <v>700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-600</v>
       </c>
-      <c r="T33" s="3">
-        <v>0</v>
-      </c>
       <c r="U33" s="3">
         <v>0</v>
       </c>
@@ -3047,13 +3119,13 @@
         <v>0</v>
       </c>
       <c r="W33" s="3">
+        <v>0</v>
+      </c>
+      <c r="X33" s="3">
         <v>-700</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-300</v>
-      </c>
-      <c r="Y33" s="3">
-        <v>-100</v>
       </c>
       <c r="Z33" s="3">
         <v>-100</v>
@@ -3065,22 +3137,25 @@
         <v>-100</v>
       </c>
       <c r="AC33" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AD33" s="3">
         <v>-300</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>600</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-500</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-200</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3174,62 +3249,65 @@
       <c r="AG34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>0</v>
+      </c>
+      <c r="E35" s="3">
         <v>-300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-1400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-100</v>
       </c>
-      <c r="I35" s="3">
-        <v>100</v>
-      </c>
       <c r="J35" s="3">
+        <v>100</v>
+      </c>
+      <c r="K35" s="3">
         <v>-600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>300</v>
       </c>
-      <c r="M35" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="N35" s="3">
+      <c r="N35" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="O35" s="3">
         <v>-100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-200</v>
       </c>
-      <c r="P35" s="3">
-        <v>100</v>
-      </c>
       <c r="Q35" s="3">
+        <v>100</v>
+      </c>
+      <c r="R35" s="3">
         <v>700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-600</v>
       </c>
-      <c r="T35" s="3">
-        <v>0</v>
-      </c>
       <c r="U35" s="3">
         <v>0</v>
       </c>
@@ -3237,13 +3315,13 @@
         <v>0</v>
       </c>
       <c r="W35" s="3">
+        <v>0</v>
+      </c>
+      <c r="X35" s="3">
         <v>-700</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-300</v>
-      </c>
-      <c r="Y35" s="3">
-        <v>-100</v>
       </c>
       <c r="Z35" s="3">
         <v>-100</v>
@@ -3255,122 +3333,128 @@
         <v>-100</v>
       </c>
       <c r="AC35" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AD35" s="3">
         <v>-300</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>600</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-500</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-200</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43738</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43646</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43555</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43465</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43373</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43281</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43190</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43100</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43008</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>42916</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42825</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42735</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42643</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3404,8 +3488,9 @@
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
-    </row>
-    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH39" s="3"/>
+    </row>
+    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3439,76 +3524,77 @@
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
-    </row>
-    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH40" s="3"/>
+    </row>
+    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E41" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F41" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="G41" s="3">
         <v>300</v>
       </c>
       <c r="H41" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="I41" s="3">
         <v>400</v>
       </c>
       <c r="J41" s="3">
+        <v>400</v>
+      </c>
+      <c r="K41" s="3">
         <v>800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>700</v>
-      </c>
-      <c r="Q41" s="3">
-        <v>800</v>
       </c>
       <c r="R41" s="3">
         <v>800</v>
       </c>
       <c r="S41" s="3">
+        <v>800</v>
+      </c>
+      <c r="T41" s="3">
         <v>700</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>900</v>
-      </c>
-      <c r="U41" s="3">
-        <v>600</v>
       </c>
       <c r="V41" s="3">
         <v>600</v>
       </c>
       <c r="W41" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="X41" s="3">
         <v>700</v>
       </c>
       <c r="Y41" s="3">
-        <v>900</v>
+        <v>700</v>
       </c>
       <c r="Z41" s="3">
         <v>900</v>
@@ -3517,25 +3603,28 @@
         <v>900</v>
       </c>
       <c r="AB41" s="3">
+        <v>900</v>
+      </c>
+      <c r="AC41" s="3">
         <v>600</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>500</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>600</v>
-      </c>
-      <c r="AE41" s="3">
-        <v>400</v>
       </c>
       <c r="AF41" s="3">
         <v>400</v>
       </c>
       <c r="AG41" s="3">
+        <v>400</v>
+      </c>
+      <c r="AH41" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3629,16 +3718,19 @@
       <c r="AG42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E43" s="3">
-        <v>0</v>
+      <c r="E43" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="F43" s="3">
         <v>0</v>
@@ -3659,46 +3751,46 @@
         <v>0</v>
       </c>
       <c r="L43" s="3">
+        <v>0</v>
+      </c>
+      <c r="M43" s="3">
         <v>500</v>
       </c>
-      <c r="M43" s="3">
-        <v>0</v>
-      </c>
       <c r="N43" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O43" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P43" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q43" s="3">
         <v>200</v>
       </c>
-      <c r="Q43" s="3">
-        <v>100</v>
-      </c>
       <c r="R43" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S43" s="3">
         <v>0</v>
       </c>
       <c r="T43" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="U43" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="V43" s="3">
         <v>200</v>
       </c>
       <c r="W43" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="X43" s="3">
         <v>100</v>
       </c>
       <c r="Y43" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Z43" s="3">
         <v>0</v>
@@ -3707,13 +3799,13 @@
         <v>0</v>
       </c>
       <c r="AB43" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC43" s="3">
         <v>200</v>
       </c>
-      <c r="AC43" s="3">
-        <v>100</v>
-      </c>
-      <c r="AD43" s="3" t="s">
-        <v>10</v>
+      <c r="AD43" s="3">
+        <v>100</v>
       </c>
       <c r="AE43" s="3" t="s">
         <v>10</v>
@@ -3724,16 +3816,19 @@
       <c r="AG43" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH43" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E44" s="3">
-        <v>0</v>
+      <c r="E44" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="F44" s="3">
         <v>0</v>
@@ -3748,10 +3843,10 @@
         <v>0</v>
       </c>
       <c r="J44" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K44" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L44" s="3">
         <v>0</v>
@@ -3760,34 +3855,34 @@
         <v>0</v>
       </c>
       <c r="N44" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O44" s="3">
         <v>100</v>
       </c>
       <c r="P44" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q44" s="3">
         <v>0</v>
       </c>
       <c r="R44" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S44" s="3">
         <v>100</v>
       </c>
       <c r="T44" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U44" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="V44" s="3">
         <v>100</v>
       </c>
       <c r="W44" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="X44" s="3">
         <v>0</v>
@@ -3796,7 +3891,7 @@
         <v>0</v>
       </c>
       <c r="Z44" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AA44" s="3">
         <v>100</v>
@@ -3808,7 +3903,7 @@
         <v>100</v>
       </c>
       <c r="AD44" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AE44" s="3">
         <v>200</v>
@@ -3819,16 +3914,19 @@
       <c r="AG44" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH44" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E45" s="3">
-        <v>0</v>
+      <c r="E45" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="F45" s="3">
         <v>0</v>
@@ -3842,8 +3940,8 @@
       <c r="I45" s="3">
         <v>0</v>
       </c>
-      <c r="J45" s="3" t="s">
-        <v>10</v>
+      <c r="J45" s="3">
+        <v>0</v>
       </c>
       <c r="K45" s="3" t="s">
         <v>10</v>
@@ -3854,11 +3952,11 @@
       <c r="M45" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="N45" s="3">
-        <v>0</v>
-      </c>
-      <c r="O45" s="3" t="s">
-        <v>10</v>
+      <c r="N45" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="O45" s="3">
+        <v>0</v>
       </c>
       <c r="P45" s="3" t="s">
         <v>10</v>
@@ -3875,8 +3973,8 @@
       <c r="T45" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="U45" s="3">
-        <v>0</v>
+      <c r="U45" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="V45" s="3">
         <v>0</v>
@@ -3914,19 +4012,22 @@
       <c r="AG45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E46" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F46" s="3">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="G46" s="3">
         <v>400</v>
@@ -3935,22 +4036,22 @@
         <v>400</v>
       </c>
       <c r="I46" s="3">
+        <v>400</v>
+      </c>
+      <c r="J46" s="3">
         <v>500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>2400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1400</v>
-      </c>
-      <c r="N46" s="3">
-        <v>1000</v>
       </c>
       <c r="O46" s="3">
         <v>1000</v>
@@ -3959,31 +4060,31 @@
         <v>1000</v>
       </c>
       <c r="Q46" s="3">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="R46" s="3">
         <v>900</v>
       </c>
       <c r="S46" s="3">
+        <v>900</v>
+      </c>
+      <c r="T46" s="3">
         <v>800</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>1100</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>900</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>800</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>900</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>700</v>
-      </c>
-      <c r="Y46" s="3">
-        <v>1000</v>
       </c>
       <c r="Z46" s="3">
         <v>1000</v>
@@ -3992,25 +4093,28 @@
         <v>1000</v>
       </c>
       <c r="AB46" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AC46" s="3">
         <v>900</v>
-      </c>
-      <c r="AC46" s="3">
-        <v>800</v>
       </c>
       <c r="AD46" s="3">
         <v>800</v>
       </c>
       <c r="AE46" s="3">
-        <v>600</v>
+        <v>800</v>
       </c>
       <c r="AF46" s="3">
         <v>600</v>
       </c>
       <c r="AG46" s="3">
+        <v>600</v>
+      </c>
+      <c r="AH46" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4021,7 +4125,7 @@
         <v>0</v>
       </c>
       <c r="F47" s="3">
-        <v>1100</v>
+        <v>0</v>
       </c>
       <c r="G47" s="3">
         <v>1100</v>
@@ -4033,14 +4137,14 @@
         <v>1100</v>
       </c>
       <c r="J47" s="3">
+        <v>1100</v>
+      </c>
+      <c r="K47" s="3">
         <v>1300</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>1200</v>
       </c>
-      <c r="L47" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="M47" s="3" t="s">
         <v>10</v>
       </c>
@@ -4056,8 +4160,8 @@
       <c r="Q47" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="R47" s="3">
-        <v>0</v>
+      <c r="R47" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="S47" s="3">
         <v>0</v>
@@ -4104,8 +4208,11 @@
       <c r="AG47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -4119,7 +4226,7 @@
         <v>100</v>
       </c>
       <c r="G48" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="H48" s="3">
         <v>200</v>
@@ -4128,25 +4235,25 @@
         <v>200</v>
       </c>
       <c r="J48" s="3">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="K48" s="3">
         <v>400</v>
       </c>
       <c r="L48" s="3">
+        <v>400</v>
+      </c>
+      <c r="M48" s="3">
         <v>700</v>
-      </c>
-      <c r="M48" s="3">
-        <v>400</v>
       </c>
       <c r="N48" s="3">
         <v>400</v>
       </c>
       <c r="O48" s="3">
+        <v>400</v>
+      </c>
+      <c r="P48" s="3">
         <v>500</v>
-      </c>
-      <c r="P48" s="3">
-        <v>400</v>
       </c>
       <c r="Q48" s="3">
         <v>400</v>
@@ -4161,7 +4268,7 @@
         <v>400</v>
       </c>
       <c r="U48" s="3">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="V48" s="3">
         <v>100</v>
@@ -4199,8 +4306,11 @@
       <c r="AG48" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH48" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4273,14 +4383,14 @@
       <c r="Z49" s="3">
         <v>0</v>
       </c>
-      <c r="AA49" s="3" t="s">
-        <v>10</v>
+      <c r="AA49" s="3">
+        <v>0</v>
       </c>
       <c r="AB49" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AC49" s="3">
-        <v>0</v>
+      <c r="AC49" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AD49" s="3">
         <v>0</v>
@@ -4294,8 +4404,11 @@
       <c r="AG49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4389,8 +4502,11 @@
       <c r="AG50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4484,8 +4600,11 @@
       <c r="AG51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4579,8 +4698,11 @@
       <c r="AG52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4674,76 +4796,79 @@
       <c r="AG53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>100</v>
+      </c>
+      <c r="E54" s="3">
         <v>200</v>
       </c>
-      <c r="E54" s="3">
-        <v>100</v>
-      </c>
       <c r="F54" s="3">
+        <v>100</v>
+      </c>
+      <c r="G54" s="3">
         <v>1600</v>
-      </c>
-      <c r="G54" s="3">
-        <v>1700</v>
       </c>
       <c r="H54" s="3">
         <v>1700</v>
       </c>
       <c r="I54" s="3">
+        <v>1700</v>
+      </c>
+      <c r="J54" s="3">
         <v>1900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>2500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>2700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>3000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1800</v>
-      </c>
-      <c r="N54" s="3">
-        <v>1500</v>
       </c>
       <c r="O54" s="3">
         <v>1500</v>
       </c>
       <c r="P54" s="3">
+        <v>1500</v>
+      </c>
+      <c r="Q54" s="3">
         <v>1400</v>
-      </c>
-      <c r="Q54" s="3">
-        <v>1300</v>
       </c>
       <c r="R54" s="3">
         <v>1300</v>
       </c>
       <c r="S54" s="3">
+        <v>1300</v>
+      </c>
+      <c r="T54" s="3">
         <v>1200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1500</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1000</v>
-      </c>
-      <c r="V54" s="3">
-        <v>900</v>
       </c>
       <c r="W54" s="3">
         <v>900</v>
       </c>
       <c r="X54" s="3">
+        <v>900</v>
+      </c>
+      <c r="Y54" s="3">
         <v>800</v>
-      </c>
-      <c r="Y54" s="3">
-        <v>1100</v>
       </c>
       <c r="Z54" s="3">
         <v>1100</v>
@@ -4755,22 +4880,25 @@
         <v>1100</v>
       </c>
       <c r="AC54" s="3">
+        <v>1100</v>
+      </c>
+      <c r="AD54" s="3">
         <v>900</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>1000</v>
-      </c>
-      <c r="AE54" s="3">
-        <v>700</v>
       </c>
       <c r="AF54" s="3">
         <v>700</v>
       </c>
       <c r="AG54" s="3">
+        <v>700</v>
+      </c>
+      <c r="AH54" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4804,8 +4932,9 @@
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
-    </row>
-    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH55" s="3"/>
+    </row>
+    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4839,8 +4968,9 @@
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
-    </row>
-    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH56" s="3"/>
+    </row>
+    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -4854,11 +4984,11 @@
         <v>100</v>
       </c>
       <c r="G57" s="3">
+        <v>100</v>
+      </c>
+      <c r="H57" s="3">
         <v>200</v>
       </c>
-      <c r="H57" s="3">
-        <v>100</v>
-      </c>
       <c r="I57" s="3">
         <v>100</v>
       </c>
@@ -4866,7 +4996,7 @@
         <v>100</v>
       </c>
       <c r="K57" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="L57" s="3">
         <v>300</v>
@@ -4878,16 +5008,16 @@
         <v>300</v>
       </c>
       <c r="O57" s="3">
+        <v>300</v>
+      </c>
+      <c r="P57" s="3">
         <v>400</v>
-      </c>
-      <c r="P57" s="3">
-        <v>300</v>
       </c>
       <c r="Q57" s="3">
         <v>300</v>
       </c>
       <c r="R57" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="S57" s="3">
         <v>100</v>
@@ -4896,13 +5026,13 @@
         <v>100</v>
       </c>
       <c r="U57" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="V57" s="3">
         <v>200</v>
       </c>
       <c r="W57" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="X57" s="3">
         <v>300</v>
@@ -4920,13 +5050,13 @@
         <v>300</v>
       </c>
       <c r="AC57" s="3">
+        <v>300</v>
+      </c>
+      <c r="AD57" s="3">
         <v>200</v>
       </c>
-      <c r="AD57" s="3">
-        <v>100</v>
-      </c>
       <c r="AE57" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AF57" s="3">
         <v>200</v>
@@ -4934,8 +5064,11 @@
       <c r="AG57" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH57" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4945,8 +5078,8 @@
       <c r="E58" s="3">
         <v>0</v>
       </c>
-      <c r="F58" s="3" t="s">
-        <v>10</v>
+      <c r="F58" s="3">
+        <v>0</v>
       </c>
       <c r="G58" s="3" t="s">
         <v>10</v>
@@ -4960,8 +5093,8 @@
       <c r="J58" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
+      <c r="K58" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="L58" s="3">
         <v>0</v>
@@ -5029,88 +5162,91 @@
       <c r="AG58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E59" s="3">
         <v>1100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>800</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>600</v>
-      </c>
-      <c r="H59" s="3">
-        <v>400</v>
       </c>
       <c r="I59" s="3">
         <v>400</v>
       </c>
       <c r="J59" s="3">
+        <v>400</v>
+      </c>
+      <c r="K59" s="3">
         <v>1400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1100</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>2100</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>1900</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>1800</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>1700</v>
-      </c>
-      <c r="V59" s="3">
-        <v>1500</v>
       </c>
       <c r="W59" s="3">
         <v>1500</v>
       </c>
       <c r="X59" s="3">
-        <v>1300</v>
+        <v>1500</v>
       </c>
       <c r="Y59" s="3">
         <v>1300</v>
       </c>
       <c r="Z59" s="3">
+        <v>1300</v>
+      </c>
+      <c r="AA59" s="3">
         <v>1200</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>1100</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>1200</v>
-      </c>
-      <c r="AC59" s="3">
-        <v>1700</v>
       </c>
       <c r="AD59" s="3">
         <v>1700</v>
@@ -5119,84 +5255,87 @@
         <v>1700</v>
       </c>
       <c r="AF59" s="3">
+        <v>1700</v>
+      </c>
+      <c r="AG59" s="3">
         <v>1500</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>1400</v>
       </c>
     </row>
-    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E60" s="3">
         <v>1200</v>
-      </c>
-      <c r="E60" s="3">
-        <v>900</v>
       </c>
       <c r="F60" s="3">
         <v>900</v>
       </c>
       <c r="G60" s="3">
+        <v>900</v>
+      </c>
+      <c r="H60" s="3">
         <v>800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>2000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1600</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>1300</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>1400</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>2200</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>2100</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>2000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>1800</v>
-      </c>
-      <c r="V60" s="3">
-        <v>1700</v>
       </c>
       <c r="W60" s="3">
         <v>1700</v>
       </c>
       <c r="X60" s="3">
-        <v>1600</v>
+        <v>1700</v>
       </c>
       <c r="Y60" s="3">
         <v>1600</v>
       </c>
       <c r="Z60" s="3">
-        <v>1500</v>
+        <v>1600</v>
       </c>
       <c r="AA60" s="3">
         <v>1500</v>
@@ -5205,22 +5344,25 @@
         <v>1500</v>
       </c>
       <c r="AC60" s="3">
+        <v>1500</v>
+      </c>
+      <c r="AD60" s="3">
         <v>1200</v>
-      </c>
-      <c r="AD60" s="3">
-        <v>1800</v>
       </c>
       <c r="AE60" s="3">
         <v>1800</v>
       </c>
       <c r="AF60" s="3">
-        <v>1600</v>
+        <v>1800</v>
       </c>
       <c r="AG60" s="3">
         <v>1600</v>
       </c>
-    </row>
-    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH60" s="3">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -5231,7 +5373,7 @@
         <v>100</v>
       </c>
       <c r="F61" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="G61" s="3">
         <v>200</v>
@@ -5246,28 +5388,28 @@
         <v>200</v>
       </c>
       <c r="K61" s="3">
+        <v>200</v>
+      </c>
+      <c r="L61" s="3">
         <v>300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>200</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>300</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>400</v>
-      </c>
-      <c r="O61" s="3">
-        <v>300</v>
       </c>
       <c r="P61" s="3">
         <v>300</v>
       </c>
       <c r="Q61" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="R61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S61" s="3">
         <v>0</v>
@@ -5314,8 +5456,11 @@
       <c r="AG61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5323,7 +5468,7 @@
         <v>0</v>
       </c>
       <c r="E62" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F62" s="3">
         <v>100</v>
@@ -5341,7 +5486,7 @@
         <v>100</v>
       </c>
       <c r="K62" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="L62" s="3">
         <v>200</v>
@@ -5359,7 +5504,7 @@
         <v>200</v>
       </c>
       <c r="Q62" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="R62" s="3">
         <v>300</v>
@@ -5370,8 +5515,8 @@
       <c r="T62" s="3">
         <v>300</v>
       </c>
-      <c r="U62" s="3" t="s">
-        <v>10</v>
+      <c r="U62" s="3">
+        <v>300</v>
       </c>
       <c r="V62" s="3" t="s">
         <v>10</v>
@@ -5388,8 +5533,8 @@
       <c r="Z62" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AA62" s="3">
-        <v>0</v>
+      <c r="AA62" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AB62" s="3">
         <v>0</v>
@@ -5409,8 +5554,11 @@
       <c r="AG62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5504,8 +5652,11 @@
       <c r="AG63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5599,8 +5750,11 @@
       <c r="AG64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5694,79 +5848,82 @@
       <c r="AG65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E66" s="3">
         <v>1400</v>
-      </c>
-      <c r="E66" s="3">
-        <v>1100</v>
       </c>
       <c r="F66" s="3">
         <v>1100</v>
       </c>
       <c r="G66" s="3">
+        <v>1100</v>
+      </c>
+      <c r="H66" s="3">
         <v>1000</v>
-      </c>
-      <c r="H66" s="3">
-        <v>800</v>
       </c>
       <c r="I66" s="3">
         <v>800</v>
       </c>
       <c r="J66" s="3">
+        <v>800</v>
+      </c>
+      <c r="K66" s="3">
         <v>1800</v>
-      </c>
-      <c r="K66" s="3">
-        <v>2300</v>
       </c>
       <c r="L66" s="3">
         <v>2300</v>
       </c>
       <c r="M66" s="3">
-        <v>2200</v>
+        <v>2300</v>
       </c>
       <c r="N66" s="3">
         <v>2200</v>
       </c>
       <c r="O66" s="3">
+        <v>2200</v>
+      </c>
+      <c r="P66" s="3">
         <v>2100</v>
-      </c>
-      <c r="P66" s="3">
-        <v>1800</v>
       </c>
       <c r="Q66" s="3">
         <v>1800</v>
       </c>
       <c r="R66" s="3">
+        <v>1800</v>
+      </c>
+      <c r="S66" s="3">
         <v>2500</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>2400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>2200</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1800</v>
-      </c>
-      <c r="V66" s="3">
-        <v>1700</v>
       </c>
       <c r="W66" s="3">
         <v>1700</v>
       </c>
       <c r="X66" s="3">
-        <v>1600</v>
+        <v>1700</v>
       </c>
       <c r="Y66" s="3">
         <v>1600</v>
       </c>
       <c r="Z66" s="3">
-        <v>1500</v>
+        <v>1600</v>
       </c>
       <c r="AA66" s="3">
         <v>1500</v>
@@ -5775,22 +5932,25 @@
         <v>1500</v>
       </c>
       <c r="AC66" s="3">
+        <v>1500</v>
+      </c>
+      <c r="AD66" s="3">
         <v>1200</v>
-      </c>
-      <c r="AD66" s="3">
-        <v>1800</v>
       </c>
       <c r="AE66" s="3">
         <v>1800</v>
       </c>
       <c r="AF66" s="3">
-        <v>1600</v>
+        <v>1800</v>
       </c>
       <c r="AG66" s="3">
         <v>1600</v>
       </c>
-    </row>
-    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH66" s="3">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5824,8 +5984,9 @@
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
-    </row>
-    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH67" s="3"/>
+    </row>
+    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5919,8 +6080,11 @@
       <c r="AG68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6014,8 +6178,11 @@
       <c r="AG69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6109,8 +6276,11 @@
       <c r="AG70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6204,61 +6374,64 @@
       <c r="AG71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-27600</v>
+      </c>
+      <c r="E72" s="3">
         <v>-27500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-27300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-25900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-25600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-25300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-25200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-25300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-24700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-24300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-24600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-24200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-24100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-23900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-24000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-24700</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-24600</v>
-      </c>
-      <c r="T72" s="3">
-        <v>-24100</v>
       </c>
       <c r="U72" s="3">
         <v>-24100</v>
@@ -6270,37 +6443,40 @@
         <v>-24100</v>
       </c>
       <c r="X72" s="3">
+        <v>-24100</v>
+      </c>
+      <c r="Y72" s="3">
         <v>-23600</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-23400</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-23300</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-23200</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-23300</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-23100</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-23500</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-23400</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-23100</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-22900</v>
       </c>
     </row>
-    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6394,8 +6570,11 @@
       <c r="AG73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6489,8 +6668,11 @@
       <c r="AG74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6584,8 +6766,11 @@
       <c r="AG75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
@@ -6593,52 +6778,52 @@
         <v>-1200</v>
       </c>
       <c r="E76" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="F76" s="3">
         <v>-900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>700</v>
-      </c>
-      <c r="H76" s="3">
-        <v>1000</v>
       </c>
       <c r="I76" s="3">
         <v>1000</v>
       </c>
       <c r="J76" s="3">
+        <v>1000</v>
+      </c>
+      <c r="K76" s="3">
         <v>700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>-400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>-800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>-600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>-400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>-500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>-1200</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>-1100</v>
-      </c>
-      <c r="T76" s="3">
-        <v>-800</v>
       </c>
       <c r="U76" s="3">
         <v>-800</v>
@@ -6653,10 +6838,10 @@
         <v>-800</v>
       </c>
       <c r="Y76" s="3">
+        <v>-800</v>
+      </c>
+      <c r="Z76" s="3">
         <v>-500</v>
-      </c>
-      <c r="Z76" s="3">
-        <v>-400</v>
       </c>
       <c r="AA76" s="3">
         <v>-400</v>
@@ -6665,22 +6850,25 @@
         <v>-400</v>
       </c>
       <c r="AC76" s="3">
+        <v>-400</v>
+      </c>
+      <c r="AD76" s="3">
         <v>-300</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>-900</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>-1200</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>-900</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6774,162 +6962,168 @@
       <c r="AG77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43738</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43646</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43555</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43465</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43373</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43281</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43190</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43100</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43008</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>42916</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42825</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42735</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42643</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>0</v>
+      </c>
+      <c r="E81" s="3">
         <v>-300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-1400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-100</v>
       </c>
-      <c r="I81" s="3">
-        <v>100</v>
-      </c>
       <c r="J81" s="3">
+        <v>100</v>
+      </c>
+      <c r="K81" s="3">
         <v>-600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>300</v>
       </c>
-      <c r="M81" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="N81" s="3">
+      <c r="N81" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="O81" s="3">
         <v>-100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-200</v>
       </c>
-      <c r="P81" s="3">
-        <v>100</v>
-      </c>
       <c r="Q81" s="3">
+        <v>100</v>
+      </c>
+      <c r="R81" s="3">
         <v>700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-600</v>
       </c>
-      <c r="T81" s="3">
-        <v>0</v>
-      </c>
       <c r="U81" s="3">
         <v>0</v>
       </c>
@@ -6937,13 +7131,13 @@
         <v>0</v>
       </c>
       <c r="W81" s="3">
+        <v>0</v>
+      </c>
+      <c r="X81" s="3">
         <v>-700</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-300</v>
-      </c>
-      <c r="Y81" s="3">
-        <v>-100</v>
       </c>
       <c r="Z81" s="3">
         <v>-100</v>
@@ -6955,22 +7149,25 @@
         <v>-100</v>
       </c>
       <c r="AC81" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AD81" s="3">
         <v>-300</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>600</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-500</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-200</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7004,28 +7201,29 @@
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
-    </row>
-    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH82" s="3"/>
+    </row>
+    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E83" s="3">
-        <v>0</v>
+      <c r="E83" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="F83" s="3">
         <v>0</v>
       </c>
-      <c r="G83" s="3" t="s">
-        <v>10</v>
+      <c r="G83" s="3">
+        <v>0</v>
       </c>
       <c r="H83" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="I83" s="3">
-        <v>0</v>
+      <c r="I83" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="J83" s="3">
         <v>0</v>
@@ -7099,8 +7297,11 @@
       <c r="AG83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7194,8 +7395,11 @@
       <c r="AG84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7289,8 +7493,11 @@
       <c r="AG85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7384,8 +7591,11 @@
       <c r="AG86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7479,8 +7689,11 @@
       <c r="AG87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7574,103 +7787,109 @@
       <c r="AG88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="E89" s="3">
+        <v>100</v>
+      </c>
+      <c r="F89" s="3">
         <v>-300</v>
       </c>
-      <c r="F89" s="3">
-        <v>0</v>
-      </c>
       <c r="G89" s="3">
         <v>0</v>
       </c>
       <c r="H89" s="3">
+        <v>0</v>
+      </c>
+      <c r="I89" s="3">
         <v>-100</v>
-      </c>
-      <c r="I89" s="3">
-        <v>-300</v>
       </c>
       <c r="J89" s="3">
         <v>-300</v>
       </c>
       <c r="K89" s="3">
-        <v>100</v>
+        <v>-300</v>
       </c>
       <c r="L89" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M89" s="3">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="N89" s="3">
         <v>-200</v>
       </c>
       <c r="O89" s="3">
+        <v>-200</v>
+      </c>
+      <c r="P89" s="3">
         <v>200</v>
-      </c>
-      <c r="P89" s="3">
-        <v>-100</v>
       </c>
       <c r="Q89" s="3">
         <v>-100</v>
       </c>
       <c r="R89" s="3">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="S89" s="3">
+        <v>100</v>
+      </c>
+      <c r="T89" s="3">
         <v>-200</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>300</v>
       </c>
-      <c r="U89" s="3">
-        <v>100</v>
-      </c>
       <c r="V89" s="3">
+        <v>100</v>
+      </c>
+      <c r="W89" s="3">
         <v>-100</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-200</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-300</v>
       </c>
-      <c r="Y89" s="3">
-        <v>100</v>
-      </c>
       <c r="Z89" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AA89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB89" s="3">
         <v>300</v>
       </c>
-      <c r="AB89" s="3">
-        <v>0</v>
-      </c>
       <c r="AC89" s="3">
         <v>0</v>
       </c>
       <c r="AD89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE89" s="3">
         <v>200</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-300</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-200</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7704,8 +7923,9 @@
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
-    </row>
-    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH90" s="3"/>
+    </row>
+    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -7734,22 +7954,22 @@
         <v>-900</v>
       </c>
       <c r="L91" s="3">
+        <v>-900</v>
+      </c>
+      <c r="M91" s="3">
         <v>-300</v>
       </c>
-      <c r="M91" s="3">
-        <v>0</v>
-      </c>
       <c r="N91" s="3">
         <v>0</v>
       </c>
       <c r="O91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="P91" s="3">
         <v>-100</v>
       </c>
-      <c r="Q91" s="3" t="s">
-        <v>10</v>
+      <c r="Q91" s="3">
+        <v>-100</v>
       </c>
       <c r="R91" s="3" t="s">
         <v>10</v>
@@ -7760,8 +7980,8 @@
       <c r="T91" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="U91" s="3">
-        <v>0</v>
+      <c r="U91" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="V91" s="3">
         <v>0</v>
@@ -7769,8 +7989,8 @@
       <c r="W91" s="3">
         <v>0</v>
       </c>
-      <c r="X91" s="3" t="s">
-        <v>10</v>
+      <c r="X91" s="3">
+        <v>0</v>
       </c>
       <c r="Y91" s="3" t="s">
         <v>10</v>
@@ -7784,23 +8004,26 @@
       <c r="AB91" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AC91" s="3">
-        <v>0</v>
+      <c r="AC91" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AD91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE91" s="3">
         <v>-100</v>
       </c>
-      <c r="AE91" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF91" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AG91" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AF91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG91" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AH91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7894,8 +8117,11 @@
       <c r="AG92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7989,16 +8215,19 @@
       <c r="AG93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E94" s="3">
-        <v>0</v>
+      <c r="E94" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="F94" s="3">
         <v>0</v>
@@ -8016,19 +8245,19 @@
         <v>0</v>
       </c>
       <c r="K94" s="3">
+        <v>0</v>
+      </c>
+      <c r="L94" s="3">
         <v>-900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-300</v>
       </c>
-      <c r="M94" s="3">
-        <v>0</v>
-      </c>
       <c r="N94" s="3">
         <v>0</v>
       </c>
       <c r="O94" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="P94" s="3">
         <v>-100</v>
@@ -8037,16 +8266,16 @@
         <v>-100</v>
       </c>
       <c r="R94" s="3">
-        <v>0</v>
-      </c>
-      <c r="S94" s="3" t="s">
-        <v>10</v>
+        <v>-100</v>
+      </c>
+      <c r="S94" s="3">
+        <v>0</v>
       </c>
       <c r="T94" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="U94" s="3">
-        <v>0</v>
+      <c r="U94" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="V94" s="3">
         <v>0</v>
@@ -8054,23 +8283,23 @@
       <c r="W94" s="3">
         <v>0</v>
       </c>
-      <c r="X94" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="Y94" s="3">
-        <v>0</v>
+      <c r="X94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y94" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="Z94" s="3">
         <v>0</v>
       </c>
-      <c r="AA94" s="3" t="s">
-        <v>10</v>
+      <c r="AA94" s="3">
+        <v>0</v>
       </c>
       <c r="AB94" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AC94" s="3">
-        <v>0</v>
+      <c r="AC94" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AD94" s="3">
         <v>0</v>
@@ -8078,14 +8307,17 @@
       <c r="AE94" s="3">
         <v>0</v>
       </c>
-      <c r="AF94" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AG94" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AF94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG94" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AH94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8119,8 +8351,9 @@
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
-    </row>
-    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH95" s="3"/>
+    </row>
+    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8214,8 +8447,11 @@
       <c r="AG96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8309,8 +8545,11 @@
       <c r="AG97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8404,8 +8643,11 @@
       <c r="AG98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8499,8 +8741,11 @@
       <c r="AG99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -8529,23 +8774,23 @@
         <v>0</v>
       </c>
       <c r="L100" s="3">
+        <v>0</v>
+      </c>
+      <c r="M100" s="3">
         <v>800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>700</v>
       </c>
-      <c r="N100" s="3">
-        <v>100</v>
-      </c>
       <c r="O100" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q100" s="3">
         <v>200</v>
       </c>
-      <c r="Q100" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="R100" s="3" t="s">
         <v>10</v>
       </c>
@@ -8561,8 +8806,8 @@
       <c r="V100" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="W100" s="3">
-        <v>0</v>
+      <c r="W100" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="X100" s="3">
         <v>0</v>
@@ -8594,8 +8839,11 @@
       <c r="AG100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8689,99 +8937,105 @@
       <c r="AG101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="E102" s="3">
+        <v>100</v>
+      </c>
+      <c r="F102" s="3">
         <v>-300</v>
       </c>
-      <c r="F102" s="3">
-        <v>0</v>
-      </c>
       <c r="G102" s="3">
         <v>0</v>
       </c>
       <c r="H102" s="3">
+        <v>0</v>
+      </c>
+      <c r="I102" s="3">
         <v>-100</v>
-      </c>
-      <c r="I102" s="3">
-        <v>-300</v>
       </c>
       <c r="J102" s="3">
         <v>-300</v>
       </c>
       <c r="K102" s="3">
+        <v>-300</v>
+      </c>
+      <c r="L102" s="3">
         <v>-800</v>
-      </c>
-      <c r="L102" s="3">
-        <v>500</v>
       </c>
       <c r="M102" s="3">
         <v>500</v>
       </c>
       <c r="N102" s="3">
+        <v>500</v>
+      </c>
+      <c r="O102" s="3">
         <v>-100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>200</v>
       </c>
-      <c r="P102" s="3">
-        <v>0</v>
-      </c>
       <c r="Q102" s="3">
+        <v>0</v>
+      </c>
+      <c r="R102" s="3">
         <v>-100</v>
       </c>
-      <c r="R102" s="3">
-        <v>100</v>
-      </c>
       <c r="S102" s="3">
+        <v>100</v>
+      </c>
+      <c r="T102" s="3">
         <v>-200</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>300</v>
       </c>
-      <c r="U102" s="3">
-        <v>100</v>
-      </c>
       <c r="V102" s="3">
+        <v>100</v>
+      </c>
+      <c r="W102" s="3">
         <v>-100</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-200</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-300</v>
       </c>
-      <c r="Y102" s="3">
-        <v>100</v>
-      </c>
       <c r="Z102" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AA102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB102" s="3">
         <v>300</v>
       </c>
-      <c r="AB102" s="3">
-        <v>0</v>
-      </c>
       <c r="AC102" s="3">
         <v>0</v>
       </c>
       <c r="AD102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE102" s="3">
         <v>200</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-300</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-200</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-100</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/CVAT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CVAT_QTR_FIN.xlsx
@@ -656,158 +656,162 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AH102"/>
+  <dimension ref="A5:AI102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43738</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43646</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43555</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43465</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43373</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43281</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43190</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43100</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43008</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42916</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42825</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42735</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42643</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>500</v>
+      </c>
+      <c r="E8" s="3">
         <v>200</v>
       </c>
-      <c r="E8" s="3">
-        <v>0</v>
-      </c>
       <c r="F8" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G8" s="3">
         <v>100</v>
@@ -816,96 +820,99 @@
         <v>100</v>
       </c>
       <c r="I8" s="3">
+        <v>100</v>
+      </c>
+      <c r="J8" s="3">
         <v>300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1000</v>
       </c>
-      <c r="K8" s="3">
-        <v>0</v>
-      </c>
       <c r="L8" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M8" s="3">
+        <v>100</v>
+      </c>
+      <c r="N8" s="3">
         <v>600</v>
       </c>
-      <c r="N8" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="O8" s="3">
-        <v>100</v>
+      <c r="O8" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="P8" s="3">
         <v>100</v>
       </c>
       <c r="Q8" s="3">
+        <v>100</v>
+      </c>
+      <c r="R8" s="3">
         <v>400</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>300</v>
       </c>
-      <c r="T8" s="3">
-        <v>0</v>
-      </c>
       <c r="U8" s="3">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="V8" s="3">
         <v>400</v>
       </c>
       <c r="W8" s="3">
+        <v>400</v>
+      </c>
+      <c r="X8" s="3">
         <v>300</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>400</v>
       </c>
-      <c r="Y8" s="3">
-        <v>100</v>
-      </c>
       <c r="Z8" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="AA8" s="3">
         <v>300</v>
       </c>
       <c r="AB8" s="3">
+        <v>300</v>
+      </c>
+      <c r="AC8" s="3">
         <v>700</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>300</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>400</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>1400</v>
       </c>
-      <c r="AF8" s="3">
-        <v>100</v>
-      </c>
       <c r="AG8" s="3">
         <v>100</v>
       </c>
       <c r="AH8" s="3">
+        <v>100</v>
+      </c>
+      <c r="AI8" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
         <v>0</v>
       </c>
-      <c r="E9" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F9" s="3">
-        <v>0</v>
+      <c r="E9" s="3">
+        <v>0</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="G9" s="3">
         <v>0</v>
@@ -914,10 +921,10 @@
         <v>0</v>
       </c>
       <c r="I9" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J9" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K9" s="3">
         <v>0</v>
@@ -946,11 +953,11 @@
       <c r="S9" s="3">
         <v>0</v>
       </c>
-      <c r="T9" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="U9" s="3">
-        <v>0</v>
+      <c r="T9" s="3">
+        <v>0</v>
+      </c>
+      <c r="U9" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="V9" s="3">
         <v>0</v>
@@ -965,10 +972,10 @@
         <v>0</v>
       </c>
       <c r="Z9" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AA9" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AB9" s="3">
         <v>0</v>
@@ -991,19 +998,22 @@
       <c r="AH9" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI9" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>500</v>
+      </c>
+      <c r="E10" s="3">
         <v>200</v>
       </c>
-      <c r="E10" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F10" s="3">
-        <v>100</v>
+      <c r="F10" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="G10" s="3">
         <v>100</v>
@@ -1012,85 +1022,88 @@
         <v>100</v>
       </c>
       <c r="I10" s="3">
+        <v>100</v>
+      </c>
+      <c r="J10" s="3">
         <v>300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1000</v>
       </c>
-      <c r="K10" s="3">
-        <v>0</v>
-      </c>
       <c r="L10" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M10" s="3">
+        <v>100</v>
+      </c>
+      <c r="N10" s="3">
         <v>600</v>
       </c>
-      <c r="N10" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="O10" s="3">
-        <v>100</v>
+      <c r="O10" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="P10" s="3">
         <v>100</v>
       </c>
       <c r="Q10" s="3">
+        <v>100</v>
+      </c>
+      <c r="R10" s="3">
         <v>400</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>1000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>300</v>
       </c>
-      <c r="T10" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="U10" s="3">
-        <v>400</v>
+      <c r="U10" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="V10" s="3">
         <v>400</v>
       </c>
       <c r="W10" s="3">
+        <v>400</v>
+      </c>
+      <c r="X10" s="3">
         <v>300</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>400</v>
       </c>
-      <c r="Y10" s="3">
-        <v>100</v>
-      </c>
       <c r="Z10" s="3">
+        <v>100</v>
+      </c>
+      <c r="AA10" s="3">
         <v>200</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>300</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>700</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>300</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>400</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>1400</v>
       </c>
-      <c r="AF10" s="3">
-        <v>100</v>
-      </c>
       <c r="AG10" s="3">
         <v>100</v>
       </c>
       <c r="AH10" s="3">
+        <v>100</v>
+      </c>
+      <c r="AI10" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1125,22 +1138,23 @@
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
-    </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI11" s="3"/>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E12" s="3">
-        <v>0</v>
+      <c r="D12" s="3">
+        <v>0</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="F12" s="3">
         <v>0</v>
       </c>
-      <c r="G12" s="3" t="s">
-        <v>10</v>
+      <c r="G12" s="3">
+        <v>0</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>10</v>
@@ -1148,8 +1162,8 @@
       <c r="I12" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="J12" s="3">
-        <v>0</v>
+      <c r="J12" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="K12" s="3">
         <v>0</v>
@@ -1157,17 +1171,17 @@
       <c r="L12" s="3">
         <v>0</v>
       </c>
-      <c r="M12" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="N12" s="3">
-        <v>0</v>
-      </c>
-      <c r="O12" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="P12" s="3">
-        <v>0</v>
+      <c r="M12" s="3">
+        <v>0</v>
+      </c>
+      <c r="N12" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="O12" s="3">
+        <v>0</v>
+      </c>
+      <c r="P12" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="Q12" s="3">
         <v>0</v>
@@ -1223,8 +1237,11 @@
       <c r="AH12" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI12" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1321,8 +1338,11 @@
       <c r="AH13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
@@ -1332,8 +1352,8 @@
       <c r="E14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F14" s="3">
-        <v>0</v>
+      <c r="F14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="G14" s="3">
         <v>0</v>
@@ -1345,20 +1365,20 @@
         <v>0</v>
       </c>
       <c r="J14" s="3">
+        <v>0</v>
+      </c>
+      <c r="K14" s="3">
         <v>200</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
       <c r="L14" s="3">
         <v>0</v>
       </c>
       <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3">
         <v>-100</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="O14" s="3" t="s">
         <v>10</v>
       </c>
@@ -1374,8 +1394,8 @@
       <c r="S14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="T14" s="3">
-        <v>0</v>
+      <c r="T14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="U14" s="3">
         <v>0</v>
@@ -1389,23 +1409,23 @@
       <c r="X14" s="3">
         <v>0</v>
       </c>
-      <c r="Y14" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="Z14" s="3">
-        <v>0</v>
+      <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AA14" s="3">
         <v>0</v>
       </c>
       <c r="AB14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC14" s="3">
         <v>-100</v>
       </c>
-      <c r="AC14" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AD14" s="3">
-        <v>0</v>
+      <c r="AD14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AE14" s="3">
         <v>0</v>
@@ -1413,14 +1433,17 @@
       <c r="AF14" s="3">
         <v>0</v>
       </c>
-      <c r="AG14" s="3" t="s">
-        <v>10</v>
+      <c r="AG14" s="3">
+        <v>0</v>
       </c>
       <c r="AH14" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI14" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1484,8 +1507,8 @@
       <c r="W15" s="3">
         <v>0</v>
       </c>
-      <c r="X15" s="3" t="s">
-        <v>10</v>
+      <c r="X15" s="3">
+        <v>0</v>
       </c>
       <c r="Y15" s="3" t="s">
         <v>10</v>
@@ -1496,8 +1519,8 @@
       <c r="AA15" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AB15" s="3">
-        <v>0</v>
+      <c r="AB15" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AC15" s="3">
         <v>0</v>
@@ -1517,8 +1540,11 @@
       <c r="AH15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1550,8 +1576,9 @@
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
-    </row>
-    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI16" s="3"/>
+    </row>
+    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1559,13 +1586,13 @@
         <v>200</v>
       </c>
       <c r="E17" s="3">
+        <v>200</v>
+      </c>
+      <c r="F17" s="3">
         <v>300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>400</v>
-      </c>
-      <c r="G17" s="3">
-        <v>300</v>
       </c>
       <c r="H17" s="3">
         <v>300</v>
@@ -1574,22 +1601,22 @@
         <v>300</v>
       </c>
       <c r="J17" s="3">
+        <v>300</v>
+      </c>
+      <c r="K17" s="3">
         <v>800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>200</v>
       </c>
-      <c r="N17" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="O17" s="3">
-        <v>300</v>
+      <c r="O17" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="P17" s="3">
         <v>300</v>
@@ -1604,150 +1631,156 @@
         <v>300</v>
       </c>
       <c r="T17" s="3">
+        <v>300</v>
+      </c>
+      <c r="U17" s="3">
         <v>600</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>300</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>400</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>300</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1100</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>300</v>
-      </c>
-      <c r="Z17" s="3">
-        <v>400</v>
       </c>
       <c r="AA17" s="3">
         <v>400</v>
       </c>
       <c r="AB17" s="3">
+        <v>400</v>
+      </c>
+      <c r="AC17" s="3">
         <v>700</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>500</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>700</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>800</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>600</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>300</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="E18" s="3">
-        <v>-300</v>
+        <v>0</v>
       </c>
       <c r="F18" s="3">
         <v>-300</v>
       </c>
       <c r="G18" s="3">
-        <v>-200</v>
+        <v>-300</v>
       </c>
       <c r="H18" s="3">
         <v>-200</v>
       </c>
       <c r="I18" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="J18" s="3">
+        <v>0</v>
+      </c>
+      <c r="K18" s="3">
         <v>200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>400</v>
       </c>
-      <c r="N18" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="O18" s="3">
-        <v>-200</v>
+      <c r="O18" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="P18" s="3">
         <v>-200</v>
       </c>
       <c r="Q18" s="3">
-        <v>100</v>
+        <v>-200</v>
       </c>
       <c r="R18" s="3">
+        <v>100</v>
+      </c>
+      <c r="S18" s="3">
         <v>700</v>
       </c>
-      <c r="S18" s="3">
-        <v>0</v>
-      </c>
       <c r="T18" s="3">
+        <v>0</v>
+      </c>
+      <c r="U18" s="3">
         <v>-600</v>
       </c>
-      <c r="U18" s="3">
-        <v>100</v>
-      </c>
       <c r="V18" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="W18" s="3">
         <v>0</v>
       </c>
       <c r="X18" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y18" s="3">
         <v>-700</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-200</v>
-      </c>
-      <c r="Z18" s="3">
-        <v>-100</v>
       </c>
       <c r="AA18" s="3">
         <v>-100</v>
       </c>
       <c r="AB18" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AC18" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD18" s="3">
         <v>-200</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-300</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>600</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-500</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>-200</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1782,8 +1815,9 @@
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
-    </row>
-    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI19" s="3"/>
+    </row>
+    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1794,10 +1828,10 @@
         <v>0</v>
       </c>
       <c r="F20" s="3">
+        <v>0</v>
+      </c>
+      <c r="G20" s="3">
         <v>-1200</v>
-      </c>
-      <c r="G20" s="3">
-        <v>-100</v>
       </c>
       <c r="H20" s="3">
         <v>-100</v>
@@ -1809,19 +1843,19 @@
         <v>-100</v>
       </c>
       <c r="K20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="L20" s="3">
         <v>-300</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
-      </c>
       <c r="M20" s="3">
         <v>0</v>
       </c>
-      <c r="N20" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="O20" s="3">
-        <v>0</v>
+      <c r="N20" s="3">
+        <v>0</v>
+      </c>
+      <c r="O20" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="P20" s="3">
         <v>0</v>
@@ -1880,65 +1914,68 @@
       <c r="AH20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>10</v>
+      <c r="D21" s="3">
+        <v>300</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F21" s="3">
+      <c r="F21" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G21" s="3">
         <v>-1400</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-200</v>
       </c>
-      <c r="H21" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="I21" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="J21" s="3">
-        <v>100</v>
+      <c r="J21" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="K21" s="3">
+        <v>100</v>
+      </c>
+      <c r="L21" s="3">
         <v>-600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>300</v>
       </c>
-      <c r="N21" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="O21" s="3">
+      <c r="O21" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="P21" s="3">
         <v>-100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-200</v>
       </c>
-      <c r="Q21" s="3">
-        <v>100</v>
-      </c>
       <c r="R21" s="3">
+        <v>100</v>
+      </c>
+      <c r="S21" s="3">
         <v>700</v>
       </c>
-      <c r="S21" s="3">
-        <v>0</v>
-      </c>
       <c r="T21" s="3">
+        <v>0</v>
+      </c>
+      <c r="U21" s="3">
         <v>-500</v>
       </c>
-      <c r="U21" s="3">
-        <v>0</v>
-      </c>
       <c r="V21" s="3">
         <v>0</v>
       </c>
@@ -1946,40 +1983,43 @@
         <v>0</v>
       </c>
       <c r="X21" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y21" s="3">
         <v>-700</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-200</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-100</v>
       </c>
-      <c r="AA21" s="3">
-        <v>0</v>
-      </c>
       <c r="AB21" s="3">
         <v>0</v>
       </c>
       <c r="AC21" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD21" s="3">
         <v>-100</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>-300</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>600</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>-500</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>-200</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2022,8 +2062,8 @@
       <c r="P22" s="3">
         <v>0</v>
       </c>
-      <c r="Q22" s="3" t="s">
-        <v>10</v>
+      <c r="Q22" s="3">
+        <v>0</v>
       </c>
       <c r="R22" s="3" t="s">
         <v>10</v>
@@ -2040,8 +2080,8 @@
       <c r="V22" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="W22" s="3">
-        <v>0</v>
+      <c r="W22" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="X22" s="3">
         <v>0</v>
@@ -2064,77 +2104,80 @@
       <c r="AD22" s="3">
         <v>0</v>
       </c>
-      <c r="AE22" s="3" t="s">
-        <v>10</v>
+      <c r="AE22" s="3">
+        <v>0</v>
       </c>
       <c r="AF22" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AG22" s="3">
-        <v>0</v>
+      <c r="AG22" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AH22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="E23" s="3">
+        <v>0</v>
+      </c>
+      <c r="F23" s="3">
         <v>-300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-1400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-100</v>
       </c>
-      <c r="J23" s="3">
-        <v>100</v>
-      </c>
       <c r="K23" s="3">
+        <v>100</v>
+      </c>
+      <c r="L23" s="3">
         <v>-600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-200</v>
       </c>
-      <c r="Q23" s="3">
-        <v>100</v>
-      </c>
       <c r="R23" s="3">
+        <v>100</v>
+      </c>
+      <c r="S23" s="3">
         <v>700</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-600</v>
       </c>
-      <c r="U23" s="3">
-        <v>0</v>
-      </c>
       <c r="V23" s="3">
         <v>0</v>
       </c>
@@ -2142,13 +2185,13 @@
         <v>0</v>
       </c>
       <c r="X23" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y23" s="3">
         <v>-700</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-300</v>
-      </c>
-      <c r="Z23" s="3">
-        <v>-100</v>
       </c>
       <c r="AA23" s="3">
         <v>-100</v>
@@ -2160,22 +2203,25 @@
         <v>-100</v>
       </c>
       <c r="AD23" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AE23" s="3">
         <v>-300</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>600</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-500</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-200</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2272,8 +2318,11 @@
       <c r="AH24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2370,65 +2419,68 @@
       <c r="AH25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="E26" s="3">
+        <v>0</v>
+      </c>
+      <c r="F26" s="3">
         <v>-300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-1400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-100</v>
       </c>
-      <c r="J26" s="3">
-        <v>100</v>
-      </c>
       <c r="K26" s="3">
+        <v>100</v>
+      </c>
+      <c r="L26" s="3">
         <v>-600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>300</v>
       </c>
-      <c r="N26" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="O26" s="3">
+      <c r="O26" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="P26" s="3">
         <v>-100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-200</v>
       </c>
-      <c r="Q26" s="3">
-        <v>100</v>
-      </c>
       <c r="R26" s="3">
+        <v>100</v>
+      </c>
+      <c r="S26" s="3">
         <v>700</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-600</v>
       </c>
-      <c r="U26" s="3">
-        <v>0</v>
-      </c>
       <c r="V26" s="3">
         <v>0</v>
       </c>
@@ -2436,13 +2488,13 @@
         <v>0</v>
       </c>
       <c r="X26" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y26" s="3">
         <v>-700</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-300</v>
-      </c>
-      <c r="Z26" s="3">
-        <v>-100</v>
       </c>
       <c r="AA26" s="3">
         <v>-100</v>
@@ -2454,79 +2506,82 @@
         <v>-100</v>
       </c>
       <c r="AD26" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AE26" s="3">
         <v>-300</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>600</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-500</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-200</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="E27" s="3">
+        <v>0</v>
+      </c>
+      <c r="F27" s="3">
         <v>-300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-1400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-100</v>
       </c>
-      <c r="J27" s="3">
-        <v>100</v>
-      </c>
       <c r="K27" s="3">
+        <v>100</v>
+      </c>
+      <c r="L27" s="3">
         <v>-600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>300</v>
       </c>
-      <c r="N27" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="O27" s="3">
+      <c r="O27" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="P27" s="3">
         <v>-100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-200</v>
       </c>
-      <c r="Q27" s="3">
-        <v>100</v>
-      </c>
       <c r="R27" s="3">
+        <v>100</v>
+      </c>
+      <c r="S27" s="3">
         <v>700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-600</v>
       </c>
-      <c r="U27" s="3">
-        <v>0</v>
-      </c>
       <c r="V27" s="3">
         <v>0</v>
       </c>
@@ -2534,13 +2589,13 @@
         <v>0</v>
       </c>
       <c r="X27" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y27" s="3">
         <v>-700</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-300</v>
-      </c>
-      <c r="Z27" s="3">
-        <v>-100</v>
       </c>
       <c r="AA27" s="3">
         <v>-100</v>
@@ -2552,22 +2607,25 @@
         <v>-100</v>
       </c>
       <c r="AD27" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AE27" s="3">
         <v>-300</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>600</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-500</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-200</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2664,8 +2722,11 @@
       <c r="AH28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2762,8 +2823,11 @@
       <c r="AH29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2860,8 +2924,11 @@
       <c r="AH30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2958,8 +3025,11 @@
       <c r="AH31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2970,11 +3040,11 @@
         <v>0</v>
       </c>
       <c r="F32" s="3">
+        <v>0</v>
+      </c>
+      <c r="G32" s="3">
         <v>1200</v>
       </c>
-      <c r="G32" s="3">
-        <v>100</v>
-      </c>
       <c r="H32" s="3">
         <v>100</v>
       </c>
@@ -2985,19 +3055,19 @@
         <v>100</v>
       </c>
       <c r="K32" s="3">
+        <v>100</v>
+      </c>
+      <c r="L32" s="3">
         <v>300</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
-      </c>
       <c r="M32" s="3">
         <v>0</v>
       </c>
-      <c r="N32" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="O32" s="3">
-        <v>0</v>
+      <c r="N32" s="3">
+        <v>0</v>
+      </c>
+      <c r="O32" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="P32" s="3">
         <v>0</v>
@@ -3056,65 +3126,68 @@
       <c r="AH32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="E33" s="3">
+        <v>0</v>
+      </c>
+      <c r="F33" s="3">
         <v>-300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-1400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-100</v>
       </c>
-      <c r="J33" s="3">
-        <v>100</v>
-      </c>
       <c r="K33" s="3">
+        <v>100</v>
+      </c>
+      <c r="L33" s="3">
         <v>-600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>300</v>
       </c>
-      <c r="N33" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="O33" s="3">
+      <c r="O33" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="P33" s="3">
         <v>-100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-200</v>
       </c>
-      <c r="Q33" s="3">
-        <v>100</v>
-      </c>
       <c r="R33" s="3">
+        <v>100</v>
+      </c>
+      <c r="S33" s="3">
         <v>700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-600</v>
       </c>
-      <c r="U33" s="3">
-        <v>0</v>
-      </c>
       <c r="V33" s="3">
         <v>0</v>
       </c>
@@ -3122,13 +3195,13 @@
         <v>0</v>
       </c>
       <c r="X33" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y33" s="3">
         <v>-700</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-300</v>
-      </c>
-      <c r="Z33" s="3">
-        <v>-100</v>
       </c>
       <c r="AA33" s="3">
         <v>-100</v>
@@ -3140,22 +3213,25 @@
         <v>-100</v>
       </c>
       <c r="AD33" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AE33" s="3">
         <v>-300</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>600</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-500</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-200</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3252,65 +3328,68 @@
       <c r="AH34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="E35" s="3">
+        <v>0</v>
+      </c>
+      <c r="F35" s="3">
         <v>-300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-1400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-100</v>
       </c>
-      <c r="J35" s="3">
-        <v>100</v>
-      </c>
       <c r="K35" s="3">
+        <v>100</v>
+      </c>
+      <c r="L35" s="3">
         <v>-600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>300</v>
       </c>
-      <c r="N35" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="O35" s="3">
+      <c r="O35" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="P35" s="3">
         <v>-100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-200</v>
       </c>
-      <c r="Q35" s="3">
-        <v>100</v>
-      </c>
       <c r="R35" s="3">
+        <v>100</v>
+      </c>
+      <c r="S35" s="3">
         <v>700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-600</v>
       </c>
-      <c r="U35" s="3">
-        <v>0</v>
-      </c>
       <c r="V35" s="3">
         <v>0</v>
       </c>
@@ -3318,13 +3397,13 @@
         <v>0</v>
       </c>
       <c r="X35" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y35" s="3">
         <v>-700</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-300</v>
-      </c>
-      <c r="Z35" s="3">
-        <v>-100</v>
       </c>
       <c r="AA35" s="3">
         <v>-100</v>
@@ -3336,125 +3415,131 @@
         <v>-100</v>
       </c>
       <c r="AD35" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AE35" s="3">
         <v>-300</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>600</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-500</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-200</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43738</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43646</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43555</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43465</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43373</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43281</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43190</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43100</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43008</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42916</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42825</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42735</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42643</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3489,8 +3574,9 @@
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
-    </row>
-    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI39" s="3"/>
+    </row>
+    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3525,79 +3611,80 @@
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
-    </row>
-    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI40" s="3"/>
+    </row>
+    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E41" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F41" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G41" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="H41" s="3">
         <v>300</v>
       </c>
       <c r="I41" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="J41" s="3">
         <v>400</v>
       </c>
       <c r="K41" s="3">
+        <v>400</v>
+      </c>
+      <c r="L41" s="3">
         <v>800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>700</v>
-      </c>
-      <c r="R41" s="3">
-        <v>800</v>
       </c>
       <c r="S41" s="3">
         <v>800</v>
       </c>
       <c r="T41" s="3">
+        <v>800</v>
+      </c>
+      <c r="U41" s="3">
         <v>700</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>900</v>
-      </c>
-      <c r="V41" s="3">
-        <v>600</v>
       </c>
       <c r="W41" s="3">
         <v>600</v>
       </c>
       <c r="X41" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="Y41" s="3">
         <v>700</v>
       </c>
       <c r="Z41" s="3">
-        <v>900</v>
+        <v>700</v>
       </c>
       <c r="AA41" s="3">
         <v>900</v>
@@ -3606,25 +3693,28 @@
         <v>900</v>
       </c>
       <c r="AC41" s="3">
+        <v>900</v>
+      </c>
+      <c r="AD41" s="3">
         <v>600</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>500</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>600</v>
-      </c>
-      <c r="AF41" s="3">
-        <v>400</v>
       </c>
       <c r="AG41" s="3">
         <v>400</v>
       </c>
       <c r="AH41" s="3">
+        <v>400</v>
+      </c>
+      <c r="AI41" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3721,19 +3811,22 @@
       <c r="AH42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3" t="s">
-        <v>10</v>
+      <c r="D43" s="3">
+        <v>0</v>
       </c>
       <c r="E43" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F43" s="3">
-        <v>0</v>
+      <c r="F43" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="G43" s="3">
         <v>0</v>
@@ -3754,46 +3847,46 @@
         <v>0</v>
       </c>
       <c r="M43" s="3">
+        <v>0</v>
+      </c>
+      <c r="N43" s="3">
         <v>500</v>
       </c>
-      <c r="N43" s="3">
-        <v>0</v>
-      </c>
       <c r="O43" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P43" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q43" s="3">
+        <v>0</v>
+      </c>
+      <c r="R43" s="3">
         <v>200</v>
       </c>
-      <c r="R43" s="3">
-        <v>100</v>
-      </c>
       <c r="S43" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T43" s="3">
         <v>0</v>
       </c>
       <c r="U43" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="V43" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="W43" s="3">
         <v>200</v>
       </c>
       <c r="X43" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="Y43" s="3">
         <v>100</v>
       </c>
       <c r="Z43" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AA43" s="3">
         <v>0</v>
@@ -3802,13 +3895,13 @@
         <v>0</v>
       </c>
       <c r="AC43" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD43" s="3">
         <v>200</v>
       </c>
-      <c r="AD43" s="3">
-        <v>100</v>
-      </c>
-      <c r="AE43" s="3" t="s">
-        <v>10</v>
+      <c r="AE43" s="3">
+        <v>100</v>
       </c>
       <c r="AF43" s="3" t="s">
         <v>10</v>
@@ -3819,8 +3912,11 @@
       <c r="AH43" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI43" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3830,8 +3926,8 @@
       <c r="E44" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F44" s="3">
-        <v>0</v>
+      <c r="F44" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="G44" s="3">
         <v>0</v>
@@ -3846,10 +3942,10 @@
         <v>0</v>
       </c>
       <c r="K44" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L44" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -3858,34 +3954,34 @@
         <v>0</v>
       </c>
       <c r="O44" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P44" s="3">
         <v>100</v>
       </c>
       <c r="Q44" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R44" s="3">
         <v>0</v>
       </c>
       <c r="S44" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="T44" s="3">
         <v>100</v>
       </c>
       <c r="U44" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V44" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="W44" s="3">
         <v>100</v>
       </c>
       <c r="X44" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Y44" s="3">
         <v>0</v>
@@ -3894,7 +3990,7 @@
         <v>0</v>
       </c>
       <c r="AA44" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AB44" s="3">
         <v>100</v>
@@ -3906,7 +4002,7 @@
         <v>100</v>
       </c>
       <c r="AE44" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AF44" s="3">
         <v>200</v>
@@ -3917,19 +4013,22 @@
       <c r="AH44" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI44" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3" t="s">
-        <v>10</v>
+      <c r="D45" s="3">
+        <v>0</v>
       </c>
       <c r="E45" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F45" s="3">
-        <v>0</v>
+      <c r="F45" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="G45" s="3">
         <v>0</v>
@@ -3943,8 +4042,8 @@
       <c r="J45" s="3">
         <v>0</v>
       </c>
-      <c r="K45" s="3" t="s">
-        <v>10</v>
+      <c r="K45" s="3">
+        <v>0</v>
       </c>
       <c r="L45" s="3" t="s">
         <v>10</v>
@@ -3955,11 +4054,11 @@
       <c r="N45" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="O45" s="3">
-        <v>0</v>
-      </c>
-      <c r="P45" s="3" t="s">
-        <v>10</v>
+      <c r="O45" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="P45" s="3">
+        <v>0</v>
       </c>
       <c r="Q45" s="3" t="s">
         <v>10</v>
@@ -3976,8 +4075,8 @@
       <c r="U45" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="V45" s="3">
-        <v>0</v>
+      <c r="V45" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="W45" s="3">
         <v>0</v>
@@ -4015,22 +4114,25 @@
       <c r="AH45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E46" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F46" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G46" s="3">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="H46" s="3">
         <v>400</v>
@@ -4039,22 +4141,22 @@
         <v>400</v>
       </c>
       <c r="J46" s="3">
+        <v>400</v>
+      </c>
+      <c r="K46" s="3">
         <v>500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>2400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1400</v>
-      </c>
-      <c r="O46" s="3">
-        <v>1000</v>
       </c>
       <c r="P46" s="3">
         <v>1000</v>
@@ -4063,31 +4165,31 @@
         <v>1000</v>
       </c>
       <c r="R46" s="3">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="S46" s="3">
         <v>900</v>
       </c>
       <c r="T46" s="3">
+        <v>900</v>
+      </c>
+      <c r="U46" s="3">
         <v>800</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>1100</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>900</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>800</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>900</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>700</v>
-      </c>
-      <c r="Z46" s="3">
-        <v>1000</v>
       </c>
       <c r="AA46" s="3">
         <v>1000</v>
@@ -4096,25 +4198,28 @@
         <v>1000</v>
       </c>
       <c r="AC46" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AD46" s="3">
         <v>900</v>
-      </c>
-      <c r="AD46" s="3">
-        <v>800</v>
       </c>
       <c r="AE46" s="3">
         <v>800</v>
       </c>
       <c r="AF46" s="3">
-        <v>600</v>
+        <v>800</v>
       </c>
       <c r="AG46" s="3">
         <v>600</v>
       </c>
       <c r="AH46" s="3">
+        <v>600</v>
+      </c>
+      <c r="AI46" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4128,7 +4233,7 @@
         <v>0</v>
       </c>
       <c r="G47" s="3">
-        <v>1100</v>
+        <v>0</v>
       </c>
       <c r="H47" s="3">
         <v>1100</v>
@@ -4140,14 +4245,14 @@
         <v>1100</v>
       </c>
       <c r="K47" s="3">
+        <v>1100</v>
+      </c>
+      <c r="L47" s="3">
         <v>1300</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>1200</v>
       </c>
-      <c r="M47" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="N47" s="3" t="s">
         <v>10</v>
       </c>
@@ -4163,8 +4268,8 @@
       <c r="R47" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="S47" s="3">
-        <v>0</v>
+      <c r="S47" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="T47" s="3">
         <v>0</v>
@@ -4211,8 +4316,11 @@
       <c r="AH47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -4229,7 +4337,7 @@
         <v>100</v>
       </c>
       <c r="H48" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="I48" s="3">
         <v>200</v>
@@ -4238,25 +4346,25 @@
         <v>200</v>
       </c>
       <c r="K48" s="3">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="L48" s="3">
         <v>400</v>
       </c>
       <c r="M48" s="3">
+        <v>400</v>
+      </c>
+      <c r="N48" s="3">
         <v>700</v>
-      </c>
-      <c r="N48" s="3">
-        <v>400</v>
       </c>
       <c r="O48" s="3">
         <v>400</v>
       </c>
       <c r="P48" s="3">
+        <v>400</v>
+      </c>
+      <c r="Q48" s="3">
         <v>500</v>
-      </c>
-      <c r="Q48" s="3">
-        <v>400</v>
       </c>
       <c r="R48" s="3">
         <v>400</v>
@@ -4271,7 +4379,7 @@
         <v>400</v>
       </c>
       <c r="V48" s="3">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="W48" s="3">
         <v>100</v>
@@ -4309,8 +4417,11 @@
       <c r="AH48" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI48" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4386,14 +4497,14 @@
       <c r="AA49" s="3">
         <v>0</v>
       </c>
-      <c r="AB49" s="3" t="s">
-        <v>10</v>
+      <c r="AB49" s="3">
+        <v>0</v>
       </c>
       <c r="AC49" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AD49" s="3">
-        <v>0</v>
+      <c r="AD49" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AE49" s="3">
         <v>0</v>
@@ -4407,8 +4518,11 @@
       <c r="AH49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4505,8 +4619,11 @@
       <c r="AH50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4603,8 +4720,11 @@
       <c r="AH51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4701,8 +4821,11 @@
       <c r="AH52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4799,79 +4922,82 @@
       <c r="AH53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="E54" s="3">
+        <v>100</v>
+      </c>
+      <c r="F54" s="3">
         <v>200</v>
       </c>
-      <c r="F54" s="3">
-        <v>100</v>
-      </c>
       <c r="G54" s="3">
+        <v>100</v>
+      </c>
+      <c r="H54" s="3">
         <v>1600</v>
-      </c>
-      <c r="H54" s="3">
-        <v>1700</v>
       </c>
       <c r="I54" s="3">
         <v>1700</v>
       </c>
       <c r="J54" s="3">
+        <v>1700</v>
+      </c>
+      <c r="K54" s="3">
         <v>1900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>2500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>2700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>3000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1800</v>
-      </c>
-      <c r="O54" s="3">
-        <v>1500</v>
       </c>
       <c r="P54" s="3">
         <v>1500</v>
       </c>
       <c r="Q54" s="3">
+        <v>1500</v>
+      </c>
+      <c r="R54" s="3">
         <v>1400</v>
-      </c>
-      <c r="R54" s="3">
-        <v>1300</v>
       </c>
       <c r="S54" s="3">
         <v>1300</v>
       </c>
       <c r="T54" s="3">
+        <v>1300</v>
+      </c>
+      <c r="U54" s="3">
         <v>1200</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1500</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1000</v>
-      </c>
-      <c r="W54" s="3">
-        <v>900</v>
       </c>
       <c r="X54" s="3">
         <v>900</v>
       </c>
       <c r="Y54" s="3">
+        <v>900</v>
+      </c>
+      <c r="Z54" s="3">
         <v>800</v>
-      </c>
-      <c r="Z54" s="3">
-        <v>1100</v>
       </c>
       <c r="AA54" s="3">
         <v>1100</v>
@@ -4883,22 +5009,25 @@
         <v>1100</v>
       </c>
       <c r="AD54" s="3">
+        <v>1100</v>
+      </c>
+      <c r="AE54" s="3">
         <v>900</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>1000</v>
-      </c>
-      <c r="AF54" s="3">
-        <v>700</v>
       </c>
       <c r="AG54" s="3">
         <v>700</v>
       </c>
       <c r="AH54" s="3">
+        <v>700</v>
+      </c>
+      <c r="AI54" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4933,8 +5062,9 @@
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
-    </row>
-    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI55" s="3"/>
+    </row>
+    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4969,8 +5099,9 @@
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
-    </row>
-    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI56" s="3"/>
+    </row>
+    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -4987,11 +5118,11 @@
         <v>100</v>
       </c>
       <c r="H57" s="3">
+        <v>100</v>
+      </c>
+      <c r="I57" s="3">
         <v>200</v>
       </c>
-      <c r="I57" s="3">
-        <v>100</v>
-      </c>
       <c r="J57" s="3">
         <v>100</v>
       </c>
@@ -4999,7 +5130,7 @@
         <v>100</v>
       </c>
       <c r="L57" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="M57" s="3">
         <v>300</v>
@@ -5011,16 +5142,16 @@
         <v>300</v>
       </c>
       <c r="P57" s="3">
+        <v>300</v>
+      </c>
+      <c r="Q57" s="3">
         <v>400</v>
-      </c>
-      <c r="Q57" s="3">
-        <v>300</v>
       </c>
       <c r="R57" s="3">
         <v>300</v>
       </c>
       <c r="S57" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="T57" s="3">
         <v>100</v>
@@ -5029,13 +5160,13 @@
         <v>100</v>
       </c>
       <c r="V57" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="W57" s="3">
         <v>200</v>
       </c>
       <c r="X57" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="Y57" s="3">
         <v>300</v>
@@ -5053,13 +5184,13 @@
         <v>300</v>
       </c>
       <c r="AD57" s="3">
+        <v>300</v>
+      </c>
+      <c r="AE57" s="3">
         <v>200</v>
       </c>
-      <c r="AE57" s="3">
-        <v>100</v>
-      </c>
       <c r="AF57" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AG57" s="3">
         <v>200</v>
@@ -5067,8 +5198,11 @@
       <c r="AH57" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI57" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -5081,8 +5215,8 @@
       <c r="F58" s="3">
         <v>0</v>
       </c>
-      <c r="G58" s="3" t="s">
-        <v>10</v>
+      <c r="G58" s="3">
+        <v>0</v>
       </c>
       <c r="H58" s="3" t="s">
         <v>10</v>
@@ -5096,8 +5230,8 @@
       <c r="K58" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L58" s="3">
-        <v>0</v>
+      <c r="L58" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="M58" s="3">
         <v>0</v>
@@ -5165,91 +5299,94 @@
       <c r="AH58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>900</v>
+      </c>
+      <c r="E59" s="3">
         <v>1000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>600</v>
-      </c>
-      <c r="I59" s="3">
-        <v>400</v>
       </c>
       <c r="J59" s="3">
         <v>400</v>
       </c>
       <c r="K59" s="3">
+        <v>400</v>
+      </c>
+      <c r="L59" s="3">
         <v>1400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>1100</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>2100</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>1900</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>1800</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>1700</v>
-      </c>
-      <c r="W59" s="3">
-        <v>1500</v>
       </c>
       <c r="X59" s="3">
         <v>1500</v>
       </c>
       <c r="Y59" s="3">
-        <v>1300</v>
+        <v>1500</v>
       </c>
       <c r="Z59" s="3">
         <v>1300</v>
       </c>
       <c r="AA59" s="3">
+        <v>1300</v>
+      </c>
+      <c r="AB59" s="3">
         <v>1200</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>1100</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>1200</v>
-      </c>
-      <c r="AD59" s="3">
-        <v>1700</v>
       </c>
       <c r="AE59" s="3">
         <v>1700</v>
@@ -5258,87 +5395,90 @@
         <v>1700</v>
       </c>
       <c r="AG59" s="3">
+        <v>1700</v>
+      </c>
+      <c r="AH59" s="3">
         <v>1500</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>1400</v>
       </c>
     </row>
-    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E60" s="3">
         <v>1100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1200</v>
-      </c>
-      <c r="F60" s="3">
-        <v>900</v>
       </c>
       <c r="G60" s="3">
         <v>900</v>
       </c>
       <c r="H60" s="3">
+        <v>900</v>
+      </c>
+      <c r="I60" s="3">
         <v>800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>2000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>1600</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>1300</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>1400</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>2200</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>2100</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>2000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>1800</v>
-      </c>
-      <c r="W60" s="3">
-        <v>1700</v>
       </c>
       <c r="X60" s="3">
         <v>1700</v>
       </c>
       <c r="Y60" s="3">
-        <v>1600</v>
+        <v>1700</v>
       </c>
       <c r="Z60" s="3">
         <v>1600</v>
       </c>
       <c r="AA60" s="3">
-        <v>1500</v>
+        <v>1600</v>
       </c>
       <c r="AB60" s="3">
         <v>1500</v>
@@ -5347,22 +5487,25 @@
         <v>1500</v>
       </c>
       <c r="AD60" s="3">
+        <v>1500</v>
+      </c>
+      <c r="AE60" s="3">
         <v>1200</v>
-      </c>
-      <c r="AE60" s="3">
-        <v>1800</v>
       </c>
       <c r="AF60" s="3">
         <v>1800</v>
       </c>
       <c r="AG60" s="3">
-        <v>1600</v>
+        <v>1800</v>
       </c>
       <c r="AH60" s="3">
         <v>1600</v>
       </c>
-    </row>
-    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI60" s="3">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -5376,7 +5519,7 @@
         <v>100</v>
       </c>
       <c r="G61" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="H61" s="3">
         <v>200</v>
@@ -5391,28 +5534,28 @@
         <v>200</v>
       </c>
       <c r="L61" s="3">
+        <v>200</v>
+      </c>
+      <c r="M61" s="3">
         <v>300</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>300</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>400</v>
-      </c>
-      <c r="P61" s="3">
-        <v>300</v>
       </c>
       <c r="Q61" s="3">
         <v>300</v>
       </c>
       <c r="R61" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="S61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T61" s="3">
         <v>0</v>
@@ -5459,8 +5602,11 @@
       <c r="AH61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5471,7 +5617,7 @@
         <v>0</v>
       </c>
       <c r="F62" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G62" s="3">
         <v>100</v>
@@ -5489,7 +5635,7 @@
         <v>100</v>
       </c>
       <c r="L62" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="M62" s="3">
         <v>200</v>
@@ -5507,7 +5653,7 @@
         <v>200</v>
       </c>
       <c r="R62" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="S62" s="3">
         <v>300</v>
@@ -5518,8 +5664,8 @@
       <c r="U62" s="3">
         <v>300</v>
       </c>
-      <c r="V62" s="3" t="s">
-        <v>10</v>
+      <c r="V62" s="3">
+        <v>300</v>
       </c>
       <c r="W62" s="3" t="s">
         <v>10</v>
@@ -5536,8 +5682,8 @@
       <c r="AA62" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AB62" s="3">
-        <v>0</v>
+      <c r="AB62" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AC62" s="3">
         <v>0</v>
@@ -5557,8 +5703,11 @@
       <c r="AH62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5655,8 +5804,11 @@
       <c r="AH63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5753,8 +5905,11 @@
       <c r="AH64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5851,82 +6006,85 @@
       <c r="AH65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E66" s="3">
         <v>1300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1400</v>
-      </c>
-      <c r="F66" s="3">
-        <v>1100</v>
       </c>
       <c r="G66" s="3">
         <v>1100</v>
       </c>
       <c r="H66" s="3">
+        <v>1100</v>
+      </c>
+      <c r="I66" s="3">
         <v>1000</v>
-      </c>
-      <c r="I66" s="3">
-        <v>800</v>
       </c>
       <c r="J66" s="3">
         <v>800</v>
       </c>
       <c r="K66" s="3">
+        <v>800</v>
+      </c>
+      <c r="L66" s="3">
         <v>1800</v>
-      </c>
-      <c r="L66" s="3">
-        <v>2300</v>
       </c>
       <c r="M66" s="3">
         <v>2300</v>
       </c>
       <c r="N66" s="3">
-        <v>2200</v>
+        <v>2300</v>
       </c>
       <c r="O66" s="3">
         <v>2200</v>
       </c>
       <c r="P66" s="3">
+        <v>2200</v>
+      </c>
+      <c r="Q66" s="3">
         <v>2100</v>
-      </c>
-      <c r="Q66" s="3">
-        <v>1800</v>
       </c>
       <c r="R66" s="3">
         <v>1800</v>
       </c>
       <c r="S66" s="3">
+        <v>1800</v>
+      </c>
+      <c r="T66" s="3">
         <v>2500</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>2400</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>2200</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1800</v>
-      </c>
-      <c r="W66" s="3">
-        <v>1700</v>
       </c>
       <c r="X66" s="3">
         <v>1700</v>
       </c>
       <c r="Y66" s="3">
-        <v>1600</v>
+        <v>1700</v>
       </c>
       <c r="Z66" s="3">
         <v>1600</v>
       </c>
       <c r="AA66" s="3">
-        <v>1500</v>
+        <v>1600</v>
       </c>
       <c r="AB66" s="3">
         <v>1500</v>
@@ -5935,22 +6093,25 @@
         <v>1500</v>
       </c>
       <c r="AD66" s="3">
+        <v>1500</v>
+      </c>
+      <c r="AE66" s="3">
         <v>1200</v>
-      </c>
-      <c r="AE66" s="3">
-        <v>1800</v>
       </c>
       <c r="AF66" s="3">
         <v>1800</v>
       </c>
       <c r="AG66" s="3">
-        <v>1600</v>
+        <v>1800</v>
       </c>
       <c r="AH66" s="3">
         <v>1600</v>
       </c>
-    </row>
-    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI66" s="3">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5985,8 +6146,9 @@
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
-    </row>
-    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI67" s="3"/>
+    </row>
+    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6083,8 +6245,11 @@
       <c r="AH68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6181,8 +6346,11 @@
       <c r="AH69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6279,8 +6447,11 @@
       <c r="AH70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6377,64 +6548,67 @@
       <c r="AH71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-27200</v>
+      </c>
+      <c r="E72" s="3">
         <v>-27600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-27500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-27300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-25900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-25600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-25300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-25200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-25300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-24700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-24300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-24600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-24200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-24100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-23900</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-24000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-24700</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-24600</v>
-      </c>
-      <c r="U72" s="3">
-        <v>-24100</v>
       </c>
       <c r="V72" s="3">
         <v>-24100</v>
@@ -6446,37 +6620,40 @@
         <v>-24100</v>
       </c>
       <c r="Y72" s="3">
+        <v>-24100</v>
+      </c>
+      <c r="Z72" s="3">
         <v>-23600</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-23400</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-23300</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-23200</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-23300</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-23100</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-23500</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-23400</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-23100</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>-22900</v>
       </c>
     </row>
-    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6573,8 +6750,11 @@
       <c r="AH73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6671,8 +6851,11 @@
       <c r="AH74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6769,64 +6952,67 @@
       <c r="AH75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>-1200</v>
+        <v>-900</v>
       </c>
       <c r="E76" s="3">
         <v>-1200</v>
       </c>
       <c r="F76" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="G76" s="3">
         <v>-900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>700</v>
-      </c>
-      <c r="I76" s="3">
-        <v>1000</v>
       </c>
       <c r="J76" s="3">
         <v>1000</v>
       </c>
       <c r="K76" s="3">
+        <v>1000</v>
+      </c>
+      <c r="L76" s="3">
         <v>700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>-400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>-800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>-600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>-400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>-500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>-1200</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>-1100</v>
-      </c>
-      <c r="U76" s="3">
-        <v>-800</v>
       </c>
       <c r="V76" s="3">
         <v>-800</v>
@@ -6841,10 +7027,10 @@
         <v>-800</v>
       </c>
       <c r="Z76" s="3">
+        <v>-800</v>
+      </c>
+      <c r="AA76" s="3">
         <v>-500</v>
-      </c>
-      <c r="AA76" s="3">
-        <v>-400</v>
       </c>
       <c r="AB76" s="3">
         <v>-400</v>
@@ -6853,22 +7039,25 @@
         <v>-400</v>
       </c>
       <c r="AD76" s="3">
+        <v>-400</v>
+      </c>
+      <c r="AE76" s="3">
         <v>-300</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>-900</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>-1200</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>-900</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6965,168 +7154,174 @@
       <c r="AH77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43738</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43646</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43555</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43465</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43373</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43281</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43190</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43100</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43008</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42916</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42825</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42735</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42643</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="E81" s="3">
+        <v>0</v>
+      </c>
+      <c r="F81" s="3">
         <v>-300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-1400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-100</v>
       </c>
-      <c r="J81" s="3">
-        <v>100</v>
-      </c>
       <c r="K81" s="3">
+        <v>100</v>
+      </c>
+      <c r="L81" s="3">
         <v>-600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>300</v>
       </c>
-      <c r="N81" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="O81" s="3">
+      <c r="O81" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="P81" s="3">
         <v>-100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-200</v>
       </c>
-      <c r="Q81" s="3">
-        <v>100</v>
-      </c>
       <c r="R81" s="3">
+        <v>100</v>
+      </c>
+      <c r="S81" s="3">
         <v>700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-600</v>
       </c>
-      <c r="U81" s="3">
-        <v>0</v>
-      </c>
       <c r="V81" s="3">
         <v>0</v>
       </c>
@@ -7134,13 +7329,13 @@
         <v>0</v>
       </c>
       <c r="X81" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y81" s="3">
         <v>-700</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-300</v>
-      </c>
-      <c r="Z81" s="3">
-        <v>-100</v>
       </c>
       <c r="AA81" s="3">
         <v>-100</v>
@@ -7152,22 +7347,25 @@
         <v>-100</v>
       </c>
       <c r="AD81" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AE81" s="3">
         <v>-300</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>600</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-500</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-200</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7202,31 +7400,32 @@
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
-    </row>
-    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI82" s="3"/>
+    </row>
+    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3" t="s">
-        <v>10</v>
+      <c r="D83" s="3">
+        <v>0</v>
       </c>
       <c r="E83" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F83" s="3">
-        <v>0</v>
+      <c r="F83" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="G83" s="3">
         <v>0</v>
       </c>
-      <c r="H83" s="3" t="s">
-        <v>10</v>
+      <c r="H83" s="3">
+        <v>0</v>
       </c>
       <c r="I83" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="J83" s="3">
-        <v>0</v>
+      <c r="J83" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="K83" s="3">
         <v>0</v>
@@ -7300,8 +7499,11 @@
       <c r="AH83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7398,8 +7600,11 @@
       <c r="AH84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7496,8 +7701,11 @@
       <c r="AH85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7594,8 +7802,11 @@
       <c r="AH86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7692,8 +7903,11 @@
       <c r="AH87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7790,106 +8004,112 @@
       <c r="AH88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>200</v>
+      </c>
+      <c r="E89" s="3">
         <v>-100</v>
       </c>
-      <c r="E89" s="3">
-        <v>100</v>
-      </c>
       <c r="F89" s="3">
+        <v>100</v>
+      </c>
+      <c r="G89" s="3">
         <v>-300</v>
       </c>
-      <c r="G89" s="3">
-        <v>0</v>
-      </c>
       <c r="H89" s="3">
         <v>0</v>
       </c>
       <c r="I89" s="3">
+        <v>0</v>
+      </c>
+      <c r="J89" s="3">
         <v>-100</v>
-      </c>
-      <c r="J89" s="3">
-        <v>-300</v>
       </c>
       <c r="K89" s="3">
         <v>-300</v>
       </c>
       <c r="L89" s="3">
-        <v>100</v>
+        <v>-300</v>
       </c>
       <c r="M89" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N89" s="3">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="O89" s="3">
         <v>-200</v>
       </c>
       <c r="P89" s="3">
+        <v>-200</v>
+      </c>
+      <c r="Q89" s="3">
         <v>200</v>
-      </c>
-      <c r="Q89" s="3">
-        <v>-100</v>
       </c>
       <c r="R89" s="3">
         <v>-100</v>
       </c>
       <c r="S89" s="3">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="T89" s="3">
+        <v>100</v>
+      </c>
+      <c r="U89" s="3">
         <v>-200</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>300</v>
       </c>
-      <c r="V89" s="3">
-        <v>100</v>
-      </c>
       <c r="W89" s="3">
+        <v>100</v>
+      </c>
+      <c r="X89" s="3">
         <v>-100</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-200</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-300</v>
       </c>
-      <c r="Z89" s="3">
-        <v>100</v>
-      </c>
       <c r="AA89" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AB89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC89" s="3">
         <v>300</v>
       </c>
-      <c r="AC89" s="3">
-        <v>0</v>
-      </c>
       <c r="AD89" s="3">
         <v>0</v>
       </c>
       <c r="AE89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF89" s="3">
         <v>200</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-300</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>-200</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7924,8 +8144,9 @@
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
-    </row>
-    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI90" s="3"/>
+    </row>
+    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -7957,22 +8178,22 @@
         <v>-900</v>
       </c>
       <c r="M91" s="3">
+        <v>-900</v>
+      </c>
+      <c r="N91" s="3">
         <v>-300</v>
       </c>
-      <c r="N91" s="3">
-        <v>0</v>
-      </c>
       <c r="O91" s="3">
         <v>0</v>
       </c>
       <c r="P91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="Q91" s="3">
         <v>-100</v>
       </c>
-      <c r="R91" s="3" t="s">
-        <v>10</v>
+      <c r="R91" s="3">
+        <v>-100</v>
       </c>
       <c r="S91" s="3" t="s">
         <v>10</v>
@@ -7983,8 +8204,8 @@
       <c r="U91" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="V91" s="3">
-        <v>0</v>
+      <c r="V91" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="W91" s="3">
         <v>0</v>
@@ -7992,8 +8213,8 @@
       <c r="X91" s="3">
         <v>0</v>
       </c>
-      <c r="Y91" s="3" t="s">
-        <v>10</v>
+      <c r="Y91" s="3">
+        <v>0</v>
       </c>
       <c r="Z91" s="3" t="s">
         <v>10</v>
@@ -8007,23 +8228,26 @@
       <c r="AC91" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AD91" s="3">
-        <v>0</v>
+      <c r="AD91" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AE91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF91" s="3">
         <v>-100</v>
       </c>
-      <c r="AF91" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG91" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AH91" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AG91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH91" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AI91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8120,8 +8344,11 @@
       <c r="AH92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8218,16 +8445,19 @@
       <c r="AH93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E94" s="3" t="s">
-        <v>10</v>
+      <c r="D94" s="3">
+        <v>0</v>
+      </c>
+      <c r="E94" s="3">
+        <v>0</v>
       </c>
       <c r="F94" s="3">
         <v>0</v>
@@ -8248,19 +8478,19 @@
         <v>0</v>
       </c>
       <c r="L94" s="3">
+        <v>0</v>
+      </c>
+      <c r="M94" s="3">
         <v>-900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-300</v>
       </c>
-      <c r="N94" s="3">
-        <v>0</v>
-      </c>
       <c r="O94" s="3">
         <v>0</v>
       </c>
       <c r="P94" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="Q94" s="3">
         <v>-100</v>
@@ -8269,16 +8499,16 @@
         <v>-100</v>
       </c>
       <c r="S94" s="3">
-        <v>0</v>
-      </c>
-      <c r="T94" s="3" t="s">
-        <v>10</v>
+        <v>-100</v>
+      </c>
+      <c r="T94" s="3">
+        <v>0</v>
       </c>
       <c r="U94" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="V94" s="3">
-        <v>0</v>
+      <c r="V94" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="W94" s="3">
         <v>0</v>
@@ -8286,23 +8516,23 @@
       <c r="X94" s="3">
         <v>0</v>
       </c>
-      <c r="Y94" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="Z94" s="3">
-        <v>0</v>
+      <c r="Y94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z94" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AA94" s="3">
         <v>0</v>
       </c>
-      <c r="AB94" s="3" t="s">
-        <v>10</v>
+      <c r="AB94" s="3">
+        <v>0</v>
       </c>
       <c r="AC94" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AD94" s="3">
-        <v>0</v>
+      <c r="AD94" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AE94" s="3">
         <v>0</v>
@@ -8310,14 +8540,17 @@
       <c r="AF94" s="3">
         <v>0</v>
       </c>
-      <c r="AG94" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AH94" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AG94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH94" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AI94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8352,8 +8585,9 @@
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
-    </row>
-    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI95" s="3"/>
+    </row>
+    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8450,8 +8684,11 @@
       <c r="AH96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8548,8 +8785,11 @@
       <c r="AH97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8646,8 +8886,11 @@
       <c r="AH98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8744,8 +8987,11 @@
       <c r="AH99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -8777,23 +9023,23 @@
         <v>0</v>
       </c>
       <c r="M100" s="3">
+        <v>0</v>
+      </c>
+      <c r="N100" s="3">
         <v>800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>700</v>
       </c>
-      <c r="O100" s="3">
-        <v>100</v>
-      </c>
       <c r="P100" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q100" s="3">
+        <v>0</v>
+      </c>
+      <c r="R100" s="3">
         <v>200</v>
       </c>
-      <c r="R100" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="S100" s="3" t="s">
         <v>10</v>
       </c>
@@ -8809,8 +9055,8 @@
       <c r="W100" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="X100" s="3">
-        <v>0</v>
+      <c r="X100" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="Y100" s="3">
         <v>0</v>
@@ -8842,8 +9088,11 @@
       <c r="AH100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8940,102 +9189,108 @@
       <c r="AH101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>200</v>
+      </c>
+      <c r="E102" s="3">
         <v>-100</v>
       </c>
-      <c r="E102" s="3">
-        <v>100</v>
-      </c>
       <c r="F102" s="3">
+        <v>100</v>
+      </c>
+      <c r="G102" s="3">
         <v>-300</v>
       </c>
-      <c r="G102" s="3">
-        <v>0</v>
-      </c>
       <c r="H102" s="3">
         <v>0</v>
       </c>
       <c r="I102" s="3">
+        <v>0</v>
+      </c>
+      <c r="J102" s="3">
         <v>-100</v>
-      </c>
-      <c r="J102" s="3">
-        <v>-300</v>
       </c>
       <c r="K102" s="3">
         <v>-300</v>
       </c>
       <c r="L102" s="3">
+        <v>-300</v>
+      </c>
+      <c r="M102" s="3">
         <v>-800</v>
-      </c>
-      <c r="M102" s="3">
-        <v>500</v>
       </c>
       <c r="N102" s="3">
         <v>500</v>
       </c>
       <c r="O102" s="3">
+        <v>500</v>
+      </c>
+      <c r="P102" s="3">
         <v>-100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>200</v>
       </c>
-      <c r="Q102" s="3">
-        <v>0</v>
-      </c>
       <c r="R102" s="3">
+        <v>0</v>
+      </c>
+      <c r="S102" s="3">
         <v>-100</v>
       </c>
-      <c r="S102" s="3">
-        <v>100</v>
-      </c>
       <c r="T102" s="3">
+        <v>100</v>
+      </c>
+      <c r="U102" s="3">
         <v>-200</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>300</v>
       </c>
-      <c r="V102" s="3">
-        <v>100</v>
-      </c>
       <c r="W102" s="3">
+        <v>100</v>
+      </c>
+      <c r="X102" s="3">
         <v>-100</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-200</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-300</v>
       </c>
-      <c r="Z102" s="3">
-        <v>100</v>
-      </c>
       <c r="AA102" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AB102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC102" s="3">
         <v>300</v>
       </c>
-      <c r="AC102" s="3">
-        <v>0</v>
-      </c>
       <c r="AD102" s="3">
         <v>0</v>
       </c>
       <c r="AE102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF102" s="3">
         <v>200</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-300</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-200</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-100</v>
       </c>
     </row>
